--- a/planningPhase/heartpigeon/heartpigeon_DB.xlsx
+++ b/planningPhase/heartpigeon/heartpigeon_DB.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TJ-BU-702-P10\Desktop\cording\kafella92.github.io\heartpigeon\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TJ-BU-702-24PC\Desktop\cording\kafella92.github.io\planningPhase\heartpigeon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52BF4180-3804-4068-9E02-418AAF7DA23A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD93BDD6-2D12-4E2C-BDB8-C31075516900}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10305" yWindow="-315" windowWidth="16245" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DB(user_gift)" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="101">
   <si>
     <t>user 선물하는사람</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -419,6 +419,18 @@
   </si>
   <si>
     <t>page</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14: 생활소모품</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기호품</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15. 인테리어</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -443,7 +455,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -522,8 +534,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -577,13 +595,28 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="hair">
+        <color auto="1"/>
+      </left>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -617,12 +650,6 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -651,6 +678,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -981,6 +1017,7 @@
     <col min="6" max="6" width="21" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="20.75" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11.625" customWidth="1"/>
+    <col min="10" max="10" width="20.375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12.375" customWidth="1"/>
     <col min="14" max="14" width="12.75" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="8.125" bestFit="1" customWidth="1"/>
@@ -1007,8 +1044,11 @@
       <c r="J2" t="s">
         <v>45</v>
       </c>
+      <c r="L2" t="s">
+        <v>99</v>
+      </c>
       <c r="M2" s="10"/>
-      <c r="N2" s="13" t="s">
+      <c r="N2" s="11" t="s">
         <v>93</v>
       </c>
       <c r="O2" s="9"/>
@@ -1031,7 +1071,7 @@
       <c r="X2" t="s">
         <v>63</v>
       </c>
-      <c r="Z2" s="21" t="s">
+      <c r="Z2" s="19" t="s">
         <v>92</v>
       </c>
     </row>
@@ -1067,19 +1107,19 @@
         <v>37</v>
       </c>
       <c r="M3" s="9"/>
-      <c r="N3" s="13" t="s">
+      <c r="N3" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="O3" s="13" t="s">
+      <c r="O3" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="P3" s="13" t="s">
+      <c r="P3" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="Q3" s="13" t="s">
+      <c r="Q3" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="R3" s="13" t="s">
+      <c r="R3" s="11" t="s">
         <v>77</v>
       </c>
       <c r="T3" s="7" t="s">
@@ -1097,18 +1137,18 @@
       <c r="X3" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="Z3" s="21" t="s">
+      <c r="Z3" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="AA3" s="21" t="s">
+      <c r="AA3" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="AB3" s="21"/>
-      <c r="AC3" s="21"/>
-      <c r="AD3" s="21"/>
-      <c r="AE3" s="21"/>
-      <c r="AF3" s="21"/>
-      <c r="AG3" s="21"/>
+      <c r="AB3" s="19"/>
+      <c r="AC3" s="19"/>
+      <c r="AD3" s="19"/>
+      <c r="AE3" s="19"/>
+      <c r="AF3" s="19"/>
+      <c r="AG3" s="19"/>
     </row>
     <row r="4" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B4" s="2"/>
@@ -1136,13 +1176,13 @@
         <v>41</v>
       </c>
       <c r="M4" s="9"/>
-      <c r="N4" s="14"/>
-      <c r="O4" s="14"/>
-      <c r="P4" s="14"/>
-      <c r="Q4" s="14" t="s">
+      <c r="N4" s="12"/>
+      <c r="O4" s="12"/>
+      <c r="P4" s="12"/>
+      <c r="Q4" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="R4" s="14" t="s">
+      <c r="R4" s="12" t="s">
         <v>39</v>
       </c>
       <c r="T4" s="8"/>
@@ -1154,14 +1194,14 @@
       </c>
       <c r="W4" s="8"/>
       <c r="X4" s="8"/>
-      <c r="Z4" s="22"/>
-      <c r="AA4" s="22"/>
-      <c r="AB4" s="22"/>
-      <c r="AC4" s="22"/>
-      <c r="AD4" s="22"/>
-      <c r="AE4" s="22"/>
-      <c r="AF4" s="22"/>
-      <c r="AG4" s="22"/>
+      <c r="Z4" s="20"/>
+      <c r="AA4" s="20"/>
+      <c r="AB4" s="20"/>
+      <c r="AC4" s="20"/>
+      <c r="AD4" s="20"/>
+      <c r="AE4" s="20"/>
+      <c r="AF4" s="20"/>
+      <c r="AG4" s="20"/>
     </row>
     <row r="5" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B5" s="2"/>
@@ -1189,13 +1229,13 @@
         <v>42</v>
       </c>
       <c r="M5" s="9"/>
-      <c r="N5" s="14"/>
-      <c r="O5" s="14"/>
-      <c r="P5" s="14"/>
-      <c r="Q5" s="14" t="s">
+      <c r="N5" s="12"/>
+      <c r="O5" s="12"/>
+      <c r="P5" s="12"/>
+      <c r="Q5" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="R5" s="14" t="s">
+      <c r="R5" s="12" t="s">
         <v>40</v>
       </c>
       <c r="T5" s="8"/>
@@ -1207,14 +1247,14 @@
       </c>
       <c r="W5" s="8"/>
       <c r="X5" s="8"/>
-      <c r="Z5" s="22"/>
-      <c r="AA5" s="22"/>
-      <c r="AB5" s="22"/>
-      <c r="AC5" s="22"/>
-      <c r="AD5" s="22"/>
-      <c r="AE5" s="22"/>
-      <c r="AF5" s="22"/>
-      <c r="AG5" s="22"/>
+      <c r="Z5" s="20"/>
+      <c r="AA5" s="20"/>
+      <c r="AB5" s="20"/>
+      <c r="AC5" s="20"/>
+      <c r="AD5" s="20"/>
+      <c r="AE5" s="20"/>
+      <c r="AF5" s="20"/>
+      <c r="AG5" s="20"/>
     </row>
     <row r="6" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B6" s="2"/>
@@ -1242,13 +1282,13 @@
         <v>43</v>
       </c>
       <c r="M6" s="9"/>
-      <c r="N6" s="14"/>
-      <c r="O6" s="14"/>
-      <c r="P6" s="14"/>
-      <c r="Q6" s="14" t="s">
+      <c r="N6" s="12"/>
+      <c r="O6" s="12"/>
+      <c r="P6" s="12"/>
+      <c r="Q6" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="R6" s="14" t="s">
+      <c r="R6" s="12" t="s">
         <v>50</v>
       </c>
       <c r="T6" s="8"/>
@@ -1260,14 +1300,14 @@
       </c>
       <c r="W6" s="8"/>
       <c r="X6" s="8"/>
-      <c r="Z6" s="22"/>
-      <c r="AA6" s="22"/>
-      <c r="AB6" s="22"/>
-      <c r="AC6" s="22"/>
-      <c r="AD6" s="22"/>
-      <c r="AE6" s="22"/>
-      <c r="AF6" s="22"/>
-      <c r="AG6" s="22"/>
+      <c r="Z6" s="20"/>
+      <c r="AA6" s="20"/>
+      <c r="AB6" s="20"/>
+      <c r="AC6" s="20"/>
+      <c r="AD6" s="20"/>
+      <c r="AE6" s="20"/>
+      <c r="AF6" s="20"/>
+      <c r="AG6" s="20"/>
     </row>
     <row r="7" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B7" s="2"/>
@@ -1289,13 +1329,13 @@
         <v>57</v>
       </c>
       <c r="M7" s="9"/>
-      <c r="N7" s="14"/>
-      <c r="O7" s="14"/>
-      <c r="P7" s="14"/>
-      <c r="Q7" s="14" t="s">
+      <c r="N7" s="12"/>
+      <c r="O7" s="12"/>
+      <c r="P7" s="12"/>
+      <c r="Q7" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="R7" s="14" t="s">
+      <c r="R7" s="12" t="s">
         <v>52</v>
       </c>
       <c r="T7" s="8"/>
@@ -1307,14 +1347,14 @@
       </c>
       <c r="W7" s="8"/>
       <c r="X7" s="8"/>
-      <c r="Z7" s="22"/>
-      <c r="AA7" s="22"/>
-      <c r="AB7" s="22"/>
-      <c r="AC7" s="22"/>
-      <c r="AD7" s="22"/>
-      <c r="AE7" s="22"/>
-      <c r="AF7" s="22"/>
-      <c r="AG7" s="22"/>
+      <c r="Z7" s="20"/>
+      <c r="AA7" s="20"/>
+      <c r="AB7" s="20"/>
+      <c r="AC7" s="20"/>
+      <c r="AD7" s="20"/>
+      <c r="AE7" s="20"/>
+      <c r="AF7" s="20"/>
+      <c r="AG7" s="20"/>
     </row>
     <row r="8" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B8" s="2"/>
@@ -1336,28 +1376,30 @@
         <v>73</v>
       </c>
       <c r="M8" s="9"/>
-      <c r="N8" s="14"/>
-      <c r="O8" s="14"/>
-      <c r="P8" s="14"/>
-      <c r="Q8" s="14" t="s">
+      <c r="N8" s="12"/>
+      <c r="O8" s="12"/>
+      <c r="P8" s="12"/>
+      <c r="Q8" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="R8" s="14" t="s">
+      <c r="R8" s="12" t="s">
         <v>51</v>
       </c>
       <c r="T8" s="8"/>
       <c r="U8" s="8"/>
-      <c r="V8" s="8"/>
+      <c r="V8" s="8" t="s">
+        <v>98</v>
+      </c>
       <c r="W8" s="8"/>
       <c r="X8" s="8"/>
-      <c r="Z8" s="22"/>
-      <c r="AA8" s="22"/>
-      <c r="AB8" s="22"/>
-      <c r="AC8" s="22"/>
-      <c r="AD8" s="22"/>
-      <c r="AE8" s="22"/>
-      <c r="AF8" s="22"/>
-      <c r="AG8" s="22"/>
+      <c r="Z8" s="20"/>
+      <c r="AA8" s="20"/>
+      <c r="AB8" s="20"/>
+      <c r="AC8" s="20"/>
+      <c r="AD8" s="20"/>
+      <c r="AE8" s="20"/>
+      <c r="AF8" s="20"/>
+      <c r="AG8" s="20"/>
     </row>
     <row r="9" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B9" s="2"/>
@@ -1377,28 +1419,30 @@
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="9"/>
-      <c r="N9" s="14"/>
-      <c r="O9" s="14"/>
-      <c r="P9" s="14"/>
-      <c r="Q9" s="14" t="s">
+      <c r="N9" s="12"/>
+      <c r="O9" s="12"/>
+      <c r="P9" s="12"/>
+      <c r="Q9" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="R9" s="14" t="s">
+      <c r="R9" s="12" t="s">
         <v>53</v>
       </c>
       <c r="T9" s="8"/>
       <c r="U9" s="8"/>
-      <c r="V9" s="8"/>
+      <c r="V9" s="8" t="s">
+        <v>100</v>
+      </c>
       <c r="W9" s="8"/>
       <c r="X9" s="8"/>
-      <c r="Z9" s="22"/>
-      <c r="AA9" s="22"/>
-      <c r="AB9" s="22"/>
-      <c r="AC9" s="22"/>
-      <c r="AD9" s="22"/>
-      <c r="AE9" s="22"/>
-      <c r="AF9" s="22"/>
-      <c r="AG9" s="22"/>
+      <c r="Z9" s="20"/>
+      <c r="AA9" s="20"/>
+      <c r="AB9" s="20"/>
+      <c r="AC9" s="20"/>
+      <c r="AD9" s="20"/>
+      <c r="AE9" s="20"/>
+      <c r="AF9" s="20"/>
+      <c r="AG9" s="20"/>
     </row>
     <row r="10" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B10" s="2"/>
@@ -1418,24 +1462,24 @@
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="9"/>
-      <c r="N10" s="14"/>
-      <c r="O10" s="14"/>
-      <c r="P10" s="14"/>
-      <c r="Q10" s="14"/>
-      <c r="R10" s="14"/>
+      <c r="N10" s="12"/>
+      <c r="O10" s="12"/>
+      <c r="P10" s="12"/>
+      <c r="Q10" s="12"/>
+      <c r="R10" s="12"/>
       <c r="T10" s="8"/>
       <c r="U10" s="8"/>
       <c r="V10" s="8"/>
       <c r="W10" s="8"/>
       <c r="X10" s="8"/>
-      <c r="Z10" s="22"/>
-      <c r="AA10" s="22"/>
-      <c r="AB10" s="22"/>
-      <c r="AC10" s="22"/>
-      <c r="AD10" s="22"/>
-      <c r="AE10" s="22"/>
-      <c r="AF10" s="22"/>
-      <c r="AG10" s="22"/>
+      <c r="Z10" s="20"/>
+      <c r="AA10" s="20"/>
+      <c r="AB10" s="20"/>
+      <c r="AC10" s="20"/>
+      <c r="AD10" s="20"/>
+      <c r="AE10" s="20"/>
+      <c r="AF10" s="20"/>
+      <c r="AG10" s="20"/>
     </row>
     <row r="11" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B11" s="2"/>
@@ -1455,24 +1499,24 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="9"/>
-      <c r="N11" s="14"/>
-      <c r="O11" s="14"/>
-      <c r="P11" s="14"/>
-      <c r="Q11" s="14"/>
-      <c r="R11" s="14"/>
+      <c r="N11" s="12"/>
+      <c r="O11" s="12"/>
+      <c r="P11" s="12"/>
+      <c r="Q11" s="12"/>
+      <c r="R11" s="12"/>
       <c r="T11" s="8"/>
       <c r="U11" s="8"/>
       <c r="V11" s="8"/>
       <c r="W11" s="8"/>
       <c r="X11" s="8"/>
-      <c r="Z11" s="22"/>
-      <c r="AA11" s="22"/>
-      <c r="AB11" s="22"/>
-      <c r="AC11" s="22"/>
-      <c r="AD11" s="22"/>
-      <c r="AE11" s="22"/>
-      <c r="AF11" s="22"/>
-      <c r="AG11" s="22"/>
+      <c r="Z11" s="20"/>
+      <c r="AA11" s="20"/>
+      <c r="AB11" s="20"/>
+      <c r="AC11" s="20"/>
+      <c r="AD11" s="20"/>
+      <c r="AE11" s="20"/>
+      <c r="AF11" s="20"/>
+      <c r="AG11" s="20"/>
     </row>
     <row r="12" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B12" s="2"/>
@@ -1492,24 +1536,24 @@
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="9"/>
-      <c r="N12" s="14"/>
-      <c r="O12" s="14"/>
-      <c r="P12" s="14"/>
-      <c r="Q12" s="14"/>
-      <c r="R12" s="14"/>
+      <c r="N12" s="12"/>
+      <c r="O12" s="12"/>
+      <c r="P12" s="12"/>
+      <c r="Q12" s="12"/>
+      <c r="R12" s="12"/>
       <c r="T12" s="8"/>
       <c r="U12" s="8"/>
       <c r="V12" s="8"/>
       <c r="W12" s="8"/>
       <c r="X12" s="8"/>
-      <c r="Z12" s="22"/>
-      <c r="AA12" s="22"/>
-      <c r="AB12" s="22"/>
-      <c r="AC12" s="22"/>
-      <c r="AD12" s="22"/>
-      <c r="AE12" s="22"/>
-      <c r="AF12" s="22"/>
-      <c r="AG12" s="22"/>
+      <c r="Z12" s="20"/>
+      <c r="AA12" s="20"/>
+      <c r="AB12" s="20"/>
+      <c r="AC12" s="20"/>
+      <c r="AD12" s="20"/>
+      <c r="AE12" s="20"/>
+      <c r="AF12" s="20"/>
+      <c r="AG12" s="20"/>
     </row>
     <row r="13" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B13" s="2"/>
@@ -1529,24 +1573,24 @@
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="9"/>
-      <c r="N13" s="14"/>
-      <c r="O13" s="14"/>
-      <c r="P13" s="14"/>
-      <c r="Q13" s="14"/>
-      <c r="R13" s="14"/>
+      <c r="N13" s="12"/>
+      <c r="O13" s="12"/>
+      <c r="P13" s="12"/>
+      <c r="Q13" s="12"/>
+      <c r="R13" s="12"/>
       <c r="T13" s="8"/>
       <c r="U13" s="8"/>
       <c r="V13" s="8"/>
       <c r="W13" s="8"/>
       <c r="X13" s="8"/>
-      <c r="Z13" s="22"/>
-      <c r="AA13" s="22"/>
-      <c r="AB13" s="22"/>
-      <c r="AC13" s="22"/>
-      <c r="AD13" s="22"/>
-      <c r="AE13" s="22"/>
-      <c r="AF13" s="22"/>
-      <c r="AG13" s="22"/>
+      <c r="Z13" s="20"/>
+      <c r="AA13" s="20"/>
+      <c r="AB13" s="20"/>
+      <c r="AC13" s="20"/>
+      <c r="AD13" s="20"/>
+      <c r="AE13" s="20"/>
+      <c r="AF13" s="20"/>
+      <c r="AG13" s="20"/>
     </row>
     <row r="14" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B14" s="2"/>
@@ -1566,24 +1610,24 @@
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="9"/>
-      <c r="N14" s="14"/>
-      <c r="O14" s="14"/>
-      <c r="P14" s="14"/>
-      <c r="Q14" s="14"/>
-      <c r="R14" s="14"/>
+      <c r="N14" s="12"/>
+      <c r="O14" s="12"/>
+      <c r="P14" s="12"/>
+      <c r="Q14" s="12"/>
+      <c r="R14" s="12"/>
       <c r="T14" s="8"/>
       <c r="U14" s="8"/>
       <c r="V14" s="8"/>
       <c r="W14" s="8"/>
       <c r="X14" s="8"/>
-      <c r="Z14" s="22"/>
-      <c r="AA14" s="22"/>
-      <c r="AB14" s="22"/>
-      <c r="AC14" s="22"/>
-      <c r="AD14" s="22"/>
-      <c r="AE14" s="22"/>
-      <c r="AF14" s="22"/>
-      <c r="AG14" s="22"/>
+      <c r="Z14" s="20"/>
+      <c r="AA14" s="20"/>
+      <c r="AB14" s="20"/>
+      <c r="AC14" s="20"/>
+      <c r="AD14" s="20"/>
+      <c r="AE14" s="20"/>
+      <c r="AF14" s="20"/>
+      <c r="AG14" s="20"/>
     </row>
     <row r="15" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B15" s="2"/>
@@ -1603,24 +1647,24 @@
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="9"/>
-      <c r="N15" s="14"/>
-      <c r="O15" s="14"/>
-      <c r="P15" s="14"/>
-      <c r="Q15" s="14"/>
-      <c r="R15" s="14"/>
+      <c r="N15" s="12"/>
+      <c r="O15" s="12"/>
+      <c r="P15" s="12"/>
+      <c r="Q15" s="12"/>
+      <c r="R15" s="12"/>
       <c r="T15" s="8"/>
       <c r="U15" s="8"/>
       <c r="V15" s="8"/>
       <c r="W15" s="8"/>
       <c r="X15" s="8"/>
-      <c r="Z15" s="22"/>
-      <c r="AA15" s="22"/>
-      <c r="AB15" s="22"/>
-      <c r="AC15" s="22"/>
-      <c r="AD15" s="22"/>
-      <c r="AE15" s="22"/>
-      <c r="AF15" s="22"/>
-      <c r="AG15" s="22"/>
+      <c r="Z15" s="20"/>
+      <c r="AA15" s="20"/>
+      <c r="AB15" s="20"/>
+      <c r="AC15" s="20"/>
+      <c r="AD15" s="20"/>
+      <c r="AE15" s="20"/>
+      <c r="AF15" s="20"/>
+      <c r="AG15" s="20"/>
     </row>
     <row r="16" spans="2:33" x14ac:dyDescent="0.3">
       <c r="T16" s="8"/>
@@ -1628,14 +1672,14 @@
       <c r="V16" s="8"/>
       <c r="W16" s="8"/>
       <c r="X16" s="8"/>
-      <c r="Z16" s="22"/>
-      <c r="AA16" s="22"/>
-      <c r="AB16" s="22"/>
-      <c r="AC16" s="22"/>
-      <c r="AD16" s="22"/>
-      <c r="AE16" s="22"/>
-      <c r="AF16" s="22"/>
-      <c r="AG16" s="22"/>
+      <c r="Z16" s="20"/>
+      <c r="AA16" s="20"/>
+      <c r="AB16" s="20"/>
+      <c r="AC16" s="20"/>
+      <c r="AD16" s="20"/>
+      <c r="AE16" s="20"/>
+      <c r="AF16" s="20"/>
+      <c r="AG16" s="20"/>
     </row>
     <row r="17" spans="9:33" x14ac:dyDescent="0.3">
       <c r="T17" s="8"/>
@@ -1643,14 +1687,14 @@
       <c r="V17" s="8"/>
       <c r="W17" s="8"/>
       <c r="X17" s="8"/>
-      <c r="Z17" s="22"/>
-      <c r="AA17" s="22"/>
-      <c r="AB17" s="22"/>
-      <c r="AC17" s="22"/>
-      <c r="AD17" s="22"/>
-      <c r="AE17" s="22"/>
-      <c r="AF17" s="22"/>
-      <c r="AG17" s="22"/>
+      <c r="Z17" s="20"/>
+      <c r="AA17" s="20"/>
+      <c r="AB17" s="20"/>
+      <c r="AC17" s="20"/>
+      <c r="AD17" s="20"/>
+      <c r="AE17" s="20"/>
+      <c r="AF17" s="20"/>
+      <c r="AG17" s="20"/>
     </row>
     <row r="18" spans="9:33" x14ac:dyDescent="0.3">
       <c r="T18" s="8"/>
@@ -1658,14 +1702,14 @@
       <c r="V18" s="8"/>
       <c r="W18" s="8"/>
       <c r="X18" s="8"/>
-      <c r="Z18" s="22"/>
-      <c r="AA18" s="22"/>
-      <c r="AB18" s="22"/>
-      <c r="AC18" s="22"/>
-      <c r="AD18" s="22"/>
-      <c r="AE18" s="22"/>
-      <c r="AF18" s="22"/>
-      <c r="AG18" s="22"/>
+      <c r="Z18" s="20"/>
+      <c r="AA18" s="20"/>
+      <c r="AB18" s="20"/>
+      <c r="AC18" s="20"/>
+      <c r="AD18" s="20"/>
+      <c r="AE18" s="20"/>
+      <c r="AF18" s="20"/>
+      <c r="AG18" s="20"/>
     </row>
     <row r="19" spans="9:33" x14ac:dyDescent="0.3">
       <c r="T19" s="8"/>
@@ -1673,14 +1717,14 @@
       <c r="V19" s="8"/>
       <c r="W19" s="8"/>
       <c r="X19" s="8"/>
-      <c r="Z19" s="22"/>
-      <c r="AA19" s="22"/>
-      <c r="AB19" s="22"/>
-      <c r="AC19" s="22"/>
-      <c r="AD19" s="22"/>
-      <c r="AE19" s="22"/>
-      <c r="AF19" s="22"/>
-      <c r="AG19" s="22"/>
+      <c r="Z19" s="20"/>
+      <c r="AA19" s="20"/>
+      <c r="AB19" s="20"/>
+      <c r="AC19" s="20"/>
+      <c r="AD19" s="20"/>
+      <c r="AE19" s="20"/>
+      <c r="AF19" s="20"/>
+      <c r="AG19" s="20"/>
     </row>
     <row r="20" spans="9:33" x14ac:dyDescent="0.3">
       <c r="T20" s="8"/>
@@ -1688,273 +1732,273 @@
       <c r="V20" s="8"/>
       <c r="W20" s="8"/>
       <c r="X20" s="8"/>
-      <c r="Z20" s="22"/>
-      <c r="AA20" s="22"/>
-      <c r="AB20" s="22"/>
-      <c r="AC20" s="22"/>
-      <c r="AD20" s="22"/>
-      <c r="AE20" s="22"/>
-      <c r="AF20" s="22"/>
-      <c r="AG20" s="22"/>
+      <c r="Z20" s="20"/>
+      <c r="AA20" s="20"/>
+      <c r="AB20" s="20"/>
+      <c r="AC20" s="20"/>
+      <c r="AD20" s="20"/>
+      <c r="AE20" s="20"/>
+      <c r="AF20" s="20"/>
+      <c r="AG20" s="20"/>
     </row>
     <row r="21" spans="9:33" x14ac:dyDescent="0.3">
-      <c r="I21" s="10"/>
-      <c r="J21" s="10"/>
-      <c r="K21" s="10"/>
-      <c r="L21" s="10"/>
-      <c r="M21" s="10"/>
-      <c r="N21" s="10"/>
-      <c r="O21" s="10"/>
-      <c r="P21" s="10"/>
-      <c r="Q21" s="10"/>
+      <c r="I21" s="21"/>
+      <c r="J21" s="21"/>
+      <c r="K21" s="21"/>
+      <c r="L21" s="21"/>
+      <c r="M21" s="21"/>
+      <c r="N21" s="21"/>
+      <c r="O21" s="21"/>
+      <c r="P21" s="21"/>
+      <c r="Q21" s="21"/>
       <c r="T21" s="8"/>
       <c r="U21" s="8"/>
       <c r="V21" s="8"/>
       <c r="W21" s="8"/>
       <c r="X21" s="8"/>
-      <c r="Z21" s="22"/>
-      <c r="AA21" s="22"/>
-      <c r="AB21" s="22"/>
-      <c r="AC21" s="22"/>
-      <c r="AD21" s="22"/>
-      <c r="AE21" s="22"/>
-      <c r="AF21" s="22"/>
-      <c r="AG21" s="22"/>
+      <c r="Z21" s="20"/>
+      <c r="AA21" s="20"/>
+      <c r="AB21" s="20"/>
+      <c r="AC21" s="20"/>
+      <c r="AD21" s="20"/>
+      <c r="AE21" s="20"/>
+      <c r="AF21" s="20"/>
+      <c r="AG21" s="20"/>
     </row>
     <row r="22" spans="9:33" x14ac:dyDescent="0.3">
-      <c r="I22" s="11"/>
-      <c r="J22" s="11"/>
-      <c r="K22" s="11"/>
-      <c r="L22" s="11"/>
-      <c r="M22" s="11"/>
-      <c r="N22" s="11"/>
-      <c r="O22" s="11"/>
-      <c r="P22" s="11"/>
-      <c r="Q22" s="11"/>
+      <c r="I22" s="21"/>
+      <c r="J22" s="21"/>
+      <c r="K22" s="21"/>
+      <c r="L22" s="21"/>
+      <c r="M22" s="21"/>
+      <c r="N22" s="21"/>
+      <c r="O22" s="21"/>
+      <c r="P22" s="21"/>
+      <c r="Q22" s="21"/>
       <c r="T22" s="8"/>
       <c r="U22" s="8"/>
       <c r="V22" s="8"/>
       <c r="W22" s="8"/>
       <c r="X22" s="8"/>
-      <c r="Z22" s="22"/>
-      <c r="AA22" s="22"/>
-      <c r="AB22" s="22"/>
-      <c r="AC22" s="22"/>
-      <c r="AD22" s="22"/>
-      <c r="AE22" s="22"/>
-      <c r="AF22" s="22"/>
-      <c r="AG22" s="22"/>
+      <c r="Z22" s="20"/>
+      <c r="AA22" s="20"/>
+      <c r="AB22" s="20"/>
+      <c r="AC22" s="20"/>
+      <c r="AD22" s="20"/>
+      <c r="AE22" s="20"/>
+      <c r="AF22" s="20"/>
+      <c r="AG22" s="20"/>
     </row>
     <row r="23" spans="9:33" x14ac:dyDescent="0.3">
-      <c r="I23" s="11"/>
-      <c r="J23" s="11"/>
-      <c r="K23" s="11"/>
-      <c r="L23" s="11"/>
-      <c r="M23" s="11"/>
-      <c r="N23" s="11"/>
-      <c r="O23" s="11"/>
-      <c r="P23" s="11"/>
-      <c r="Q23" s="11"/>
+      <c r="I23" s="21"/>
+      <c r="J23" s="21"/>
+      <c r="K23" s="21"/>
+      <c r="L23" s="21"/>
+      <c r="M23" s="21"/>
+      <c r="N23" s="21"/>
+      <c r="O23" s="21"/>
+      <c r="P23" s="21"/>
+      <c r="Q23" s="21"/>
       <c r="T23" s="8"/>
       <c r="U23" s="8"/>
       <c r="V23" s="8"/>
       <c r="W23" s="8"/>
       <c r="X23" s="8"/>
-      <c r="Z23" s="22"/>
-      <c r="AA23" s="22"/>
-      <c r="AB23" s="22"/>
-      <c r="AC23" s="22"/>
-      <c r="AD23" s="22"/>
-      <c r="AE23" s="22"/>
-      <c r="AF23" s="22"/>
-      <c r="AG23" s="22"/>
+      <c r="Z23" s="20"/>
+      <c r="AA23" s="20"/>
+      <c r="AB23" s="20"/>
+      <c r="AC23" s="20"/>
+      <c r="AD23" s="20"/>
+      <c r="AE23" s="20"/>
+      <c r="AF23" s="20"/>
+      <c r="AG23" s="20"/>
     </row>
     <row r="24" spans="9:33" x14ac:dyDescent="0.3">
-      <c r="I24" s="11"/>
-      <c r="J24" s="11"/>
-      <c r="K24" s="11"/>
-      <c r="L24" s="11"/>
-      <c r="M24" s="11"/>
-      <c r="N24" s="11"/>
-      <c r="O24" s="11"/>
-      <c r="P24" s="11"/>
-      <c r="Q24" s="11"/>
+      <c r="I24" s="21"/>
+      <c r="J24" s="21"/>
+      <c r="K24" s="21"/>
+      <c r="L24" s="21"/>
+      <c r="M24" s="21"/>
+      <c r="N24" s="21"/>
+      <c r="O24" s="21"/>
+      <c r="P24" s="21"/>
+      <c r="Q24" s="21"/>
     </row>
     <row r="25" spans="9:33" x14ac:dyDescent="0.3">
-      <c r="I25" s="11"/>
-      <c r="J25" s="11"/>
-      <c r="K25" s="11"/>
-      <c r="L25" s="11"/>
-      <c r="M25" s="11"/>
-      <c r="N25" s="11"/>
-      <c r="O25" s="11"/>
-      <c r="P25" s="11"/>
-      <c r="Q25" s="11"/>
+      <c r="I25" s="21"/>
+      <c r="J25" s="21"/>
+      <c r="K25" s="21"/>
+      <c r="L25" s="21"/>
+      <c r="M25" s="21"/>
+      <c r="N25" s="21"/>
+      <c r="O25" s="21"/>
+      <c r="P25" s="21"/>
+      <c r="Q25" s="21"/>
     </row>
     <row r="26" spans="9:33" x14ac:dyDescent="0.3">
-      <c r="I26" s="11"/>
-      <c r="J26" s="11"/>
-      <c r="K26" s="11"/>
-      <c r="L26" s="11"/>
-      <c r="M26" s="11"/>
-      <c r="N26" s="11"/>
-      <c r="O26" s="11"/>
-      <c r="P26" s="11"/>
-      <c r="Q26" s="11"/>
+      <c r="I26" s="21"/>
+      <c r="J26" s="21"/>
+      <c r="K26" s="21"/>
+      <c r="L26" s="21"/>
+      <c r="M26" s="21"/>
+      <c r="N26" s="21"/>
+      <c r="O26" s="21"/>
+      <c r="P26" s="21"/>
+      <c r="Q26" s="21"/>
     </row>
     <row r="27" spans="9:33" x14ac:dyDescent="0.3">
-      <c r="I27" s="11"/>
-      <c r="J27" s="11"/>
-      <c r="K27" s="11"/>
-      <c r="L27" s="11"/>
-      <c r="M27" s="11"/>
-      <c r="N27" s="11"/>
-      <c r="O27" s="11"/>
-      <c r="P27" s="11"/>
-      <c r="Q27" s="11"/>
+      <c r="I27" s="21"/>
+      <c r="J27" s="21"/>
+      <c r="K27" s="21"/>
+      <c r="L27" s="21"/>
+      <c r="M27" s="21"/>
+      <c r="N27" s="21"/>
+      <c r="O27" s="21"/>
+      <c r="P27" s="21"/>
+      <c r="Q27" s="21"/>
     </row>
     <row r="28" spans="9:33" x14ac:dyDescent="0.3">
-      <c r="I28" s="11"/>
-      <c r="J28" s="11"/>
-      <c r="K28" s="11"/>
-      <c r="L28" s="11"/>
-      <c r="M28" s="11"/>
-      <c r="N28" s="11"/>
-      <c r="O28" s="11"/>
-      <c r="P28" s="11"/>
-      <c r="Q28" s="11"/>
+      <c r="I28" s="21"/>
+      <c r="J28" s="21"/>
+      <c r="K28" s="21"/>
+      <c r="L28" s="21"/>
+      <c r="M28" s="21"/>
+      <c r="N28" s="21"/>
+      <c r="O28" s="21"/>
+      <c r="P28" s="21"/>
+      <c r="Q28" s="21"/>
     </row>
     <row r="29" spans="9:33" x14ac:dyDescent="0.3">
-      <c r="I29" s="11"/>
-      <c r="J29" s="11"/>
-      <c r="K29" s="11"/>
-      <c r="L29" s="11"/>
-      <c r="M29" s="11"/>
-      <c r="N29" s="11"/>
-      <c r="O29" s="11"/>
-      <c r="P29" s="11"/>
-      <c r="Q29" s="11"/>
+      <c r="I29" s="21"/>
+      <c r="J29" s="21"/>
+      <c r="K29" s="21"/>
+      <c r="L29" s="21"/>
+      <c r="M29" s="21"/>
+      <c r="N29" s="21"/>
+      <c r="O29" s="21"/>
+      <c r="P29" s="21"/>
+      <c r="Q29" s="21"/>
     </row>
     <row r="30" spans="9:33" x14ac:dyDescent="0.3">
-      <c r="I30" s="11"/>
-      <c r="J30" s="11"/>
-      <c r="K30" s="11"/>
-      <c r="L30" s="11"/>
-      <c r="M30" s="11"/>
-      <c r="N30" s="11"/>
-      <c r="O30" s="11"/>
-      <c r="P30" s="11"/>
-      <c r="Q30" s="11"/>
+      <c r="I30" s="21"/>
+      <c r="J30" s="21"/>
+      <c r="K30" s="21"/>
+      <c r="L30" s="21"/>
+      <c r="M30" s="21"/>
+      <c r="N30" s="21"/>
+      <c r="O30" s="21"/>
+      <c r="P30" s="21"/>
+      <c r="Q30" s="21"/>
     </row>
     <row r="31" spans="9:33" x14ac:dyDescent="0.3">
-      <c r="I31" s="11"/>
-      <c r="J31" s="11"/>
-      <c r="K31" s="11"/>
-      <c r="L31" s="11"/>
-      <c r="M31" s="11"/>
-      <c r="N31" s="11"/>
-      <c r="O31" s="11"/>
-      <c r="P31" s="11"/>
-      <c r="Q31" s="11"/>
+      <c r="I31" s="21"/>
+      <c r="J31" s="21"/>
+      <c r="K31" s="21"/>
+      <c r="L31" s="21"/>
+      <c r="M31" s="21"/>
+      <c r="N31" s="21"/>
+      <c r="O31" s="21"/>
+      <c r="P31" s="21"/>
+      <c r="Q31" s="21"/>
     </row>
     <row r="32" spans="9:33" x14ac:dyDescent="0.3">
-      <c r="I32" s="11"/>
-      <c r="J32" s="11"/>
-      <c r="K32" s="11"/>
-      <c r="L32" s="11"/>
-      <c r="M32" s="11"/>
-      <c r="N32" s="11"/>
-      <c r="O32" s="11"/>
-      <c r="P32" s="11"/>
-      <c r="Q32" s="11"/>
+      <c r="I32" s="21"/>
+      <c r="J32" s="21"/>
+      <c r="K32" s="21"/>
+      <c r="L32" s="21"/>
+      <c r="M32" s="21"/>
+      <c r="N32" s="21"/>
+      <c r="O32" s="21"/>
+      <c r="P32" s="21"/>
+      <c r="Q32" s="21"/>
     </row>
     <row r="33" spans="9:17" x14ac:dyDescent="0.3">
-      <c r="I33" s="11"/>
-      <c r="J33" s="11"/>
-      <c r="K33" s="11"/>
-      <c r="L33" s="11"/>
-      <c r="M33" s="11"/>
-      <c r="N33" s="11"/>
-      <c r="O33" s="11"/>
-      <c r="P33" s="11"/>
-      <c r="Q33" s="11"/>
+      <c r="I33" s="21"/>
+      <c r="J33" s="21"/>
+      <c r="K33" s="21"/>
+      <c r="L33" s="21"/>
+      <c r="M33" s="21"/>
+      <c r="N33" s="21"/>
+      <c r="O33" s="21"/>
+      <c r="P33" s="21"/>
+      <c r="Q33" s="21"/>
     </row>
     <row r="34" spans="9:17" x14ac:dyDescent="0.3">
-      <c r="I34" s="11"/>
-      <c r="J34" s="11"/>
-      <c r="K34" s="11"/>
-      <c r="L34" s="11"/>
-      <c r="M34" s="11"/>
-      <c r="N34" s="11"/>
-      <c r="O34" s="11"/>
-      <c r="P34" s="11"/>
-      <c r="Q34" s="11"/>
+      <c r="I34" s="21"/>
+      <c r="J34" s="21"/>
+      <c r="K34" s="21"/>
+      <c r="L34" s="21"/>
+      <c r="M34" s="21"/>
+      <c r="N34" s="21"/>
+      <c r="O34" s="21"/>
+      <c r="P34" s="21"/>
+      <c r="Q34" s="21"/>
     </row>
     <row r="35" spans="9:17" x14ac:dyDescent="0.3">
-      <c r="I35" s="11"/>
-      <c r="J35" s="11"/>
-      <c r="K35" s="11"/>
-      <c r="L35" s="11"/>
-      <c r="M35" s="11"/>
-      <c r="N35" s="11"/>
-      <c r="O35" s="11"/>
-      <c r="P35" s="11"/>
-      <c r="Q35" s="11"/>
+      <c r="I35" s="21"/>
+      <c r="J35" s="21"/>
+      <c r="K35" s="21"/>
+      <c r="L35" s="21"/>
+      <c r="M35" s="21"/>
+      <c r="N35" s="21"/>
+      <c r="O35" s="21"/>
+      <c r="P35" s="21"/>
+      <c r="Q35" s="21"/>
     </row>
     <row r="36" spans="9:17" x14ac:dyDescent="0.3">
-      <c r="I36" s="11"/>
-      <c r="J36" s="11"/>
-      <c r="K36" s="11"/>
-      <c r="L36" s="11"/>
-      <c r="M36" s="11"/>
-      <c r="N36" s="11"/>
-      <c r="O36" s="11"/>
-      <c r="P36" s="11"/>
-      <c r="Q36" s="11"/>
+      <c r="I36" s="21"/>
+      <c r="J36" s="21"/>
+      <c r="K36" s="21"/>
+      <c r="L36" s="21"/>
+      <c r="M36" s="21"/>
+      <c r="N36" s="21"/>
+      <c r="O36" s="21"/>
+      <c r="P36" s="21"/>
+      <c r="Q36" s="21"/>
     </row>
     <row r="37" spans="9:17" x14ac:dyDescent="0.3">
-      <c r="I37" s="11"/>
-      <c r="J37" s="11"/>
-      <c r="K37" s="11"/>
-      <c r="L37" s="11"/>
-      <c r="M37" s="11"/>
-      <c r="N37" s="11"/>
-      <c r="O37" s="11"/>
-      <c r="P37" s="11"/>
-      <c r="Q37" s="11"/>
+      <c r="I37" s="21"/>
+      <c r="J37" s="21"/>
+      <c r="K37" s="21"/>
+      <c r="L37" s="21"/>
+      <c r="M37" s="21"/>
+      <c r="N37" s="21"/>
+      <c r="O37" s="21"/>
+      <c r="P37" s="21"/>
+      <c r="Q37" s="21"/>
     </row>
     <row r="38" spans="9:17" x14ac:dyDescent="0.3">
-      <c r="I38" s="11"/>
-      <c r="J38" s="11"/>
-      <c r="K38" s="11"/>
-      <c r="L38" s="11"/>
-      <c r="M38" s="11"/>
-      <c r="N38" s="11"/>
-      <c r="O38" s="11"/>
-      <c r="P38" s="11"/>
-      <c r="Q38" s="11"/>
+      <c r="I38" s="21"/>
+      <c r="J38" s="21"/>
+      <c r="K38" s="21"/>
+      <c r="L38" s="21"/>
+      <c r="M38" s="21"/>
+      <c r="N38" s="21"/>
+      <c r="O38" s="21"/>
+      <c r="P38" s="21"/>
+      <c r="Q38" s="21"/>
     </row>
     <row r="39" spans="9:17" x14ac:dyDescent="0.3">
-      <c r="I39" s="11"/>
-      <c r="J39" s="11"/>
-      <c r="K39" s="11"/>
-      <c r="L39" s="11"/>
-      <c r="M39" s="11"/>
-      <c r="N39" s="11"/>
-      <c r="O39" s="11"/>
-      <c r="P39" s="11"/>
-      <c r="Q39" s="11"/>
+      <c r="I39" s="21"/>
+      <c r="J39" s="21"/>
+      <c r="K39" s="21"/>
+      <c r="L39" s="21"/>
+      <c r="M39" s="21"/>
+      <c r="N39" s="21"/>
+      <c r="O39" s="21"/>
+      <c r="P39" s="21"/>
+      <c r="Q39" s="21"/>
     </row>
     <row r="40" spans="9:17" x14ac:dyDescent="0.3">
-      <c r="I40" s="12"/>
-      <c r="J40" s="12"/>
-      <c r="K40" s="12"/>
-      <c r="L40" s="12"/>
-      <c r="M40" s="12"/>
-      <c r="N40" s="12"/>
-      <c r="O40" s="12"/>
-      <c r="P40" s="12"/>
-      <c r="Q40" s="12"/>
+      <c r="I40" s="22"/>
+      <c r="J40" s="22"/>
+      <c r="K40" s="22"/>
+      <c r="L40" s="22"/>
+      <c r="M40" s="22"/>
+      <c r="N40" s="22"/>
+      <c r="O40" s="22"/>
+      <c r="P40" s="22"/>
+      <c r="Q40" s="22"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1974,7 +2018,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="17" t="s">
         <v>84</v>
       </c>
       <c r="F2" t="s">
@@ -1982,82 +2026,82 @@
       </c>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="F3" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="G3" s="20"/>
+      <c r="G3" s="18"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B4" s="18"/>
-      <c r="C4" s="18" t="s">
+      <c r="B4" s="16"/>
+      <c r="C4" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="D4" s="18">
+      <c r="D4" s="16">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B5" s="18"/>
-      <c r="C5" s="18" t="s">
+      <c r="B5" s="16"/>
+      <c r="C5" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="16">
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="18"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B14" s="18"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/planningPhase/heartpigeon/heartpigeon_DB.xlsx
+++ b/planningPhase/heartpigeon/heartpigeon_DB.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TJ-BU-702-P10\Desktop\cording\kafella92.github.io\heartpigeon\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52BF4180-3804-4068-9E02-418AAF7DA23A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="10305" yWindow="-315" windowWidth="16245" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10308" yWindow="-312" windowWidth="16248" windowHeight="11388"/>
   </bookViews>
   <sheets>
     <sheet name="DB(user_gift)" sheetId="1" r:id="rId1"/>
@@ -28,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="99">
   <si>
     <t>user 선물하는사람</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -419,13 +413,17 @@
   </si>
   <si>
     <t>page</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스코빌이니까 한국 제품 많이 넣어보기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -718,7 +716,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -770,7 +768,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -964,37 +962,37 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:AG40"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="17.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.875" customWidth="1"/>
+    <col min="2" max="2" width="17.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.8984375" customWidth="1"/>
     <col min="5" max="5" width="11.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="21" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.75" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.625" customWidth="1"/>
-    <col min="11" max="11" width="12.375" customWidth="1"/>
-    <col min="14" max="14" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="23.125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.69921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.59765625" customWidth="1"/>
+    <col min="11" max="11" width="12.3984375" customWidth="1"/>
+    <col min="14" max="14" width="12.69921875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.09765625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.59765625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="23.09765625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.09765625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.19921875" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="34.5" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="17.375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="23.75" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.19921875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="17.3984375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="23.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:33" x14ac:dyDescent="0.4">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1034,8 +1032,11 @@
       <c r="Z2" s="21" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="3" spans="2:33" x14ac:dyDescent="0.3">
+      <c r="AA2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="3" spans="2:33" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
@@ -1110,7 +1111,7 @@
       <c r="AF3" s="21"/>
       <c r="AG3" s="21"/>
     </row>
-    <row r="4" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:33" x14ac:dyDescent="0.4">
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
@@ -1163,7 +1164,7 @@
       <c r="AF4" s="22"/>
       <c r="AG4" s="22"/>
     </row>
-    <row r="5" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:33" x14ac:dyDescent="0.4">
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2" t="s">
@@ -1216,7 +1217,7 @@
       <c r="AF5" s="22"/>
       <c r="AG5" s="22"/>
     </row>
-    <row r="6" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:33" x14ac:dyDescent="0.4">
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2" t="s">
@@ -1269,7 +1270,7 @@
       <c r="AF6" s="22"/>
       <c r="AG6" s="22"/>
     </row>
-    <row r="7" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:33" x14ac:dyDescent="0.4">
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2" t="s">
@@ -1316,7 +1317,7 @@
       <c r="AF7" s="22"/>
       <c r="AG7" s="22"/>
     </row>
-    <row r="8" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:33" x14ac:dyDescent="0.4">
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2" t="s">
@@ -1359,7 +1360,7 @@
       <c r="AF8" s="22"/>
       <c r="AG8" s="22"/>
     </row>
-    <row r="9" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:33" x14ac:dyDescent="0.4">
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2" t="s">
@@ -1400,7 +1401,7 @@
       <c r="AF9" s="22"/>
       <c r="AG9" s="22"/>
     </row>
-    <row r="10" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:33" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2" t="s">
@@ -1437,7 +1438,7 @@
       <c r="AF10" s="22"/>
       <c r="AG10" s="22"/>
     </row>
-    <row r="11" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:33" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2" t="s">
@@ -1474,7 +1475,7 @@
       <c r="AF11" s="22"/>
       <c r="AG11" s="22"/>
     </row>
-    <row r="12" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:33" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2" t="s">
@@ -1511,7 +1512,7 @@
       <c r="AF12" s="22"/>
       <c r="AG12" s="22"/>
     </row>
-    <row r="13" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:33" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2" t="s">
@@ -1548,7 +1549,7 @@
       <c r="AF13" s="22"/>
       <c r="AG13" s="22"/>
     </row>
-    <row r="14" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:33" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2" t="s">
@@ -1585,7 +1586,7 @@
       <c r="AF14" s="22"/>
       <c r="AG14" s="22"/>
     </row>
-    <row r="15" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:33" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2" t="s">
@@ -1622,7 +1623,7 @@
       <c r="AF15" s="22"/>
       <c r="AG15" s="22"/>
     </row>
-    <row r="16" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:33" ht="16.5" x14ac:dyDescent="0.3">
       <c r="T16" s="8"/>
       <c r="U16" s="8"/>
       <c r="V16" s="8"/>
@@ -1637,7 +1638,7 @@
       <c r="AF16" s="22"/>
       <c r="AG16" s="22"/>
     </row>
-    <row r="17" spans="9:33" x14ac:dyDescent="0.3">
+    <row r="17" spans="9:33" ht="16.5" x14ac:dyDescent="0.3">
       <c r="T17" s="8"/>
       <c r="U17" s="8"/>
       <c r="V17" s="8"/>
@@ -1652,7 +1653,7 @@
       <c r="AF17" s="22"/>
       <c r="AG17" s="22"/>
     </row>
-    <row r="18" spans="9:33" x14ac:dyDescent="0.3">
+    <row r="18" spans="9:33" ht="16.5" x14ac:dyDescent="0.3">
       <c r="T18" s="8"/>
       <c r="U18" s="8"/>
       <c r="V18" s="8"/>
@@ -1667,7 +1668,7 @@
       <c r="AF18" s="22"/>
       <c r="AG18" s="22"/>
     </row>
-    <row r="19" spans="9:33" x14ac:dyDescent="0.3">
+    <row r="19" spans="9:33" ht="16.5" x14ac:dyDescent="0.3">
       <c r="T19" s="8"/>
       <c r="U19" s="8"/>
       <c r="V19" s="8"/>
@@ -1682,7 +1683,7 @@
       <c r="AF19" s="22"/>
       <c r="AG19" s="22"/>
     </row>
-    <row r="20" spans="9:33" x14ac:dyDescent="0.3">
+    <row r="20" spans="9:33" ht="16.5" x14ac:dyDescent="0.3">
       <c r="T20" s="8"/>
       <c r="U20" s="8"/>
       <c r="V20" s="8"/>
@@ -1697,7 +1698,7 @@
       <c r="AF20" s="22"/>
       <c r="AG20" s="22"/>
     </row>
-    <row r="21" spans="9:33" x14ac:dyDescent="0.3">
+    <row r="21" spans="9:33" ht="16.5" x14ac:dyDescent="0.3">
       <c r="I21" s="10"/>
       <c r="J21" s="10"/>
       <c r="K21" s="10"/>
@@ -1721,7 +1722,7 @@
       <c r="AF21" s="22"/>
       <c r="AG21" s="22"/>
     </row>
-    <row r="22" spans="9:33" x14ac:dyDescent="0.3">
+    <row r="22" spans="9:33" ht="16.5" x14ac:dyDescent="0.3">
       <c r="I22" s="11"/>
       <c r="J22" s="11"/>
       <c r="K22" s="11"/>
@@ -1745,7 +1746,7 @@
       <c r="AF22" s="22"/>
       <c r="AG22" s="22"/>
     </row>
-    <row r="23" spans="9:33" x14ac:dyDescent="0.3">
+    <row r="23" spans="9:33" ht="16.5" x14ac:dyDescent="0.3">
       <c r="I23" s="11"/>
       <c r="J23" s="11"/>
       <c r="K23" s="11"/>
@@ -1769,7 +1770,7 @@
       <c r="AF23" s="22"/>
       <c r="AG23" s="22"/>
     </row>
-    <row r="24" spans="9:33" x14ac:dyDescent="0.3">
+    <row r="24" spans="9:33" ht="16.5" x14ac:dyDescent="0.3">
       <c r="I24" s="11"/>
       <c r="J24" s="11"/>
       <c r="K24" s="11"/>
@@ -1780,7 +1781,7 @@
       <c r="P24" s="11"/>
       <c r="Q24" s="11"/>
     </row>
-    <row r="25" spans="9:33" x14ac:dyDescent="0.3">
+    <row r="25" spans="9:33" ht="16.5" x14ac:dyDescent="0.3">
       <c r="I25" s="11"/>
       <c r="J25" s="11"/>
       <c r="K25" s="11"/>
@@ -1791,7 +1792,7 @@
       <c r="P25" s="11"/>
       <c r="Q25" s="11"/>
     </row>
-    <row r="26" spans="9:33" x14ac:dyDescent="0.3">
+    <row r="26" spans="9:33" ht="16.5" x14ac:dyDescent="0.3">
       <c r="I26" s="11"/>
       <c r="J26" s="11"/>
       <c r="K26" s="11"/>
@@ -1802,7 +1803,7 @@
       <c r="P26" s="11"/>
       <c r="Q26" s="11"/>
     </row>
-    <row r="27" spans="9:33" x14ac:dyDescent="0.3">
+    <row r="27" spans="9:33" ht="16.5" x14ac:dyDescent="0.3">
       <c r="I27" s="11"/>
       <c r="J27" s="11"/>
       <c r="K27" s="11"/>
@@ -1813,7 +1814,7 @@
       <c r="P27" s="11"/>
       <c r="Q27" s="11"/>
     </row>
-    <row r="28" spans="9:33" x14ac:dyDescent="0.3">
+    <row r="28" spans="9:33" ht="16.5" x14ac:dyDescent="0.3">
       <c r="I28" s="11"/>
       <c r="J28" s="11"/>
       <c r="K28" s="11"/>
@@ -1824,7 +1825,7 @@
       <c r="P28" s="11"/>
       <c r="Q28" s="11"/>
     </row>
-    <row r="29" spans="9:33" x14ac:dyDescent="0.3">
+    <row r="29" spans="9:33" ht="16.5" x14ac:dyDescent="0.3">
       <c r="I29" s="11"/>
       <c r="J29" s="11"/>
       <c r="K29" s="11"/>
@@ -1835,7 +1836,7 @@
       <c r="P29" s="11"/>
       <c r="Q29" s="11"/>
     </row>
-    <row r="30" spans="9:33" x14ac:dyDescent="0.3">
+    <row r="30" spans="9:33" ht="16.5" x14ac:dyDescent="0.3">
       <c r="I30" s="11"/>
       <c r="J30" s="11"/>
       <c r="K30" s="11"/>
@@ -1846,7 +1847,7 @@
       <c r="P30" s="11"/>
       <c r="Q30" s="11"/>
     </row>
-    <row r="31" spans="9:33" x14ac:dyDescent="0.3">
+    <row r="31" spans="9:33" ht="16.5" x14ac:dyDescent="0.3">
       <c r="I31" s="11"/>
       <c r="J31" s="11"/>
       <c r="K31" s="11"/>
@@ -1857,7 +1858,7 @@
       <c r="P31" s="11"/>
       <c r="Q31" s="11"/>
     </row>
-    <row r="32" spans="9:33" x14ac:dyDescent="0.3">
+    <row r="32" spans="9:33" ht="16.5" x14ac:dyDescent="0.3">
       <c r="I32" s="11"/>
       <c r="J32" s="11"/>
       <c r="K32" s="11"/>
@@ -1868,7 +1869,7 @@
       <c r="P32" s="11"/>
       <c r="Q32" s="11"/>
     </row>
-    <row r="33" spans="9:17" x14ac:dyDescent="0.3">
+    <row r="33" spans="9:17" ht="16.5" x14ac:dyDescent="0.3">
       <c r="I33" s="11"/>
       <c r="J33" s="11"/>
       <c r="K33" s="11"/>
@@ -1879,7 +1880,7 @@
       <c r="P33" s="11"/>
       <c r="Q33" s="11"/>
     </row>
-    <row r="34" spans="9:17" x14ac:dyDescent="0.3">
+    <row r="34" spans="9:17" ht="16.5" x14ac:dyDescent="0.3">
       <c r="I34" s="11"/>
       <c r="J34" s="11"/>
       <c r="K34" s="11"/>
@@ -1890,7 +1891,7 @@
       <c r="P34" s="11"/>
       <c r="Q34" s="11"/>
     </row>
-    <row r="35" spans="9:17" x14ac:dyDescent="0.3">
+    <row r="35" spans="9:17" ht="16.5" x14ac:dyDescent="0.3">
       <c r="I35" s="11"/>
       <c r="J35" s="11"/>
       <c r="K35" s="11"/>
@@ -1901,7 +1902,7 @@
       <c r="P35" s="11"/>
       <c r="Q35" s="11"/>
     </row>
-    <row r="36" spans="9:17" x14ac:dyDescent="0.3">
+    <row r="36" spans="9:17" x14ac:dyDescent="0.4">
       <c r="I36" s="11"/>
       <c r="J36" s="11"/>
       <c r="K36" s="11"/>
@@ -1912,7 +1913,7 @@
       <c r="P36" s="11"/>
       <c r="Q36" s="11"/>
     </row>
-    <row r="37" spans="9:17" x14ac:dyDescent="0.3">
+    <row r="37" spans="9:17" x14ac:dyDescent="0.4">
       <c r="I37" s="11"/>
       <c r="J37" s="11"/>
       <c r="K37" s="11"/>
@@ -1923,7 +1924,7 @@
       <c r="P37" s="11"/>
       <c r="Q37" s="11"/>
     </row>
-    <row r="38" spans="9:17" x14ac:dyDescent="0.3">
+    <row r="38" spans="9:17" x14ac:dyDescent="0.4">
       <c r="I38" s="11"/>
       <c r="J38" s="11"/>
       <c r="K38" s="11"/>
@@ -1934,7 +1935,7 @@
       <c r="P38" s="11"/>
       <c r="Q38" s="11"/>
     </row>
-    <row r="39" spans="9:17" x14ac:dyDescent="0.3">
+    <row r="39" spans="9:17" x14ac:dyDescent="0.4">
       <c r="I39" s="11"/>
       <c r="J39" s="11"/>
       <c r="K39" s="11"/>
@@ -1945,7 +1946,7 @@
       <c r="P39" s="11"/>
       <c r="Q39" s="11"/>
     </row>
-    <row r="40" spans="9:17" x14ac:dyDescent="0.3">
+    <row r="40" spans="9:17" x14ac:dyDescent="0.4">
       <c r="I40" s="12"/>
       <c r="J40" s="12"/>
       <c r="K40" s="12"/>
@@ -1964,16 +1965,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB14CF65-C935-4081-8098-F1DF22D1ECCF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:G14"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="63" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B2" s="19" t="s">
         <v>84</v>
       </c>
@@ -1981,7 +1982,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:7" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B3" s="15" t="s">
         <v>87</v>
       </c>
@@ -1996,7 +1997,7 @@
       </c>
       <c r="G3" s="20"/>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B4" s="18"/>
       <c r="C4" s="18" t="s">
         <v>88</v>
@@ -2005,7 +2006,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B5" s="18"/>
       <c r="C5" s="18" t="s">
         <v>89</v>
@@ -2014,47 +2015,47 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:7" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
       <c r="D6" s="18"/>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:7" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B7" s="18"/>
       <c r="C7" s="18"/>
       <c r="D7" s="18"/>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:7" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B8" s="18"/>
       <c r="C8" s="18"/>
       <c r="D8" s="18"/>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:7" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B9" s="18"/>
       <c r="C9" s="18"/>
       <c r="D9" s="18"/>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:7" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B10" s="18"/>
       <c r="C10" s="18"/>
       <c r="D10" s="18"/>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:7" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B11" s="18"/>
       <c r="C11" s="18"/>
       <c r="D11" s="18"/>
     </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:7" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B12" s="18"/>
       <c r="C12" s="18"/>
       <c r="D12" s="18"/>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:7" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B13" s="18"/>
       <c r="C13" s="18"/>
       <c r="D13" s="18"/>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:7" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B14" s="18"/>
       <c r="C14" s="18"/>
       <c r="D14" s="18"/>
@@ -2066,9 +2067,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2076,9 +2077,9 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/planningPhase/heartpigeon/heartpigeon_DB.xlsx
+++ b/planningPhase/heartpigeon/heartpigeon_DB.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TJ-BU-702-24PC\Desktop\cording\kafella92.github.io\planningPhase\heartpigeon\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26529F8B-9021-4B35-881E-CA1FC292CE80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10308" yWindow="-312" windowWidth="16248" windowHeight="11388"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DB(user_gift)" sheetId="1" r:id="rId1"/>
@@ -22,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="108">
   <si>
     <t>user 선물하는사람</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -388,10 +394,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ano</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>printRule 출력 조합 규칙</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -417,13 +419,53 @@
   </si>
   <si>
     <t>스코빌이니까 한국 제품 많이 넣어보기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ano (PK)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>질문순서</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>atext</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>score</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nextQuestionNo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ltone</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lplace</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ltempleate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Letter 편지 양식</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lno (PK)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -441,7 +483,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -520,6 +562,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="5">
     <border>
@@ -642,13 +690,13 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -962,37 +1010,37 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:AG40"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="17.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.8984375" customWidth="1"/>
+    <col min="2" max="2" width="17.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.875" customWidth="1"/>
     <col min="5" max="5" width="11.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="21" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.69921875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.59765625" customWidth="1"/>
-    <col min="11" max="11" width="12.3984375" customWidth="1"/>
-    <col min="14" max="14" width="12.69921875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.09765625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.59765625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="23.09765625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.09765625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.19921875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.75" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.625" customWidth="1"/>
+    <col min="11" max="11" width="12.375" customWidth="1"/>
+    <col min="14" max="14" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="23.125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.25" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="34.5" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.19921875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="17.3984375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="23.69921875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="17.375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="23.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:33" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1007,7 +1055,7 @@
       </c>
       <c r="M2" s="10"/>
       <c r="N2" s="13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O2" s="9"/>
       <c r="P2" s="9"/>
@@ -1029,14 +1077,14 @@
       <c r="X2" t="s">
         <v>63</v>
       </c>
-      <c r="Z2" s="21" t="s">
-        <v>92</v>
+      <c r="Z2" s="20" t="s">
+        <v>91</v>
       </c>
       <c r="AA2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="3" spans="2:33" ht="16.5" x14ac:dyDescent="0.3">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="3" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
@@ -1072,10 +1120,10 @@
         <v>75</v>
       </c>
       <c r="O3" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="P3" s="13" t="s">
         <v>94</v>
-      </c>
-      <c r="P3" s="13" t="s">
-        <v>95</v>
       </c>
       <c r="Q3" s="13" t="s">
         <v>76</v>
@@ -1098,20 +1146,20 @@
       <c r="X3" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="Z3" s="21" t="s">
+      <c r="Z3" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="AA3" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="AA3" s="21" t="s">
-        <v>97</v>
-      </c>
-      <c r="AB3" s="21"/>
-      <c r="AC3" s="21"/>
-      <c r="AD3" s="21"/>
-      <c r="AE3" s="21"/>
-      <c r="AF3" s="21"/>
-      <c r="AG3" s="21"/>
-    </row>
-    <row r="4" spans="2:33" x14ac:dyDescent="0.4">
+      <c r="AB3" s="20"/>
+      <c r="AC3" s="20"/>
+      <c r="AD3" s="20"/>
+      <c r="AE3" s="20"/>
+      <c r="AF3" s="20"/>
+      <c r="AG3" s="20"/>
+    </row>
+    <row r="4" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
@@ -1155,16 +1203,16 @@
       </c>
       <c r="W4" s="8"/>
       <c r="X4" s="8"/>
-      <c r="Z4" s="22"/>
-      <c r="AA4" s="22"/>
-      <c r="AB4" s="22"/>
-      <c r="AC4" s="22"/>
-      <c r="AD4" s="22"/>
-      <c r="AE4" s="22"/>
-      <c r="AF4" s="22"/>
-      <c r="AG4" s="22"/>
-    </row>
-    <row r="5" spans="2:33" x14ac:dyDescent="0.4">
+      <c r="Z4" s="21"/>
+      <c r="AA4" s="21"/>
+      <c r="AB4" s="21"/>
+      <c r="AC4" s="21"/>
+      <c r="AD4" s="21"/>
+      <c r="AE4" s="21"/>
+      <c r="AF4" s="21"/>
+      <c r="AG4" s="21"/>
+    </row>
+    <row r="5" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2" t="s">
@@ -1208,16 +1256,16 @@
       </c>
       <c r="W5" s="8"/>
       <c r="X5" s="8"/>
-      <c r="Z5" s="22"/>
-      <c r="AA5" s="22"/>
-      <c r="AB5" s="22"/>
-      <c r="AC5" s="22"/>
-      <c r="AD5" s="22"/>
-      <c r="AE5" s="22"/>
-      <c r="AF5" s="22"/>
-      <c r="AG5" s="22"/>
-    </row>
-    <row r="6" spans="2:33" x14ac:dyDescent="0.4">
+      <c r="Z5" s="21"/>
+      <c r="AA5" s="21"/>
+      <c r="AB5" s="21"/>
+      <c r="AC5" s="21"/>
+      <c r="AD5" s="21"/>
+      <c r="AE5" s="21"/>
+      <c r="AF5" s="21"/>
+      <c r="AG5" s="21"/>
+    </row>
+    <row r="6" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2" t="s">
@@ -1261,16 +1309,16 @@
       </c>
       <c r="W6" s="8"/>
       <c r="X6" s="8"/>
-      <c r="Z6" s="22"/>
-      <c r="AA6" s="22"/>
-      <c r="AB6" s="22"/>
-      <c r="AC6" s="22"/>
-      <c r="AD6" s="22"/>
-      <c r="AE6" s="22"/>
-      <c r="AF6" s="22"/>
-      <c r="AG6" s="22"/>
-    </row>
-    <row r="7" spans="2:33" x14ac:dyDescent="0.4">
+      <c r="Z6" s="21"/>
+      <c r="AA6" s="21"/>
+      <c r="AB6" s="21"/>
+      <c r="AC6" s="21"/>
+      <c r="AD6" s="21"/>
+      <c r="AE6" s="21"/>
+      <c r="AF6" s="21"/>
+      <c r="AG6" s="21"/>
+    </row>
+    <row r="7" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2" t="s">
@@ -1308,16 +1356,16 @@
       </c>
       <c r="W7" s="8"/>
       <c r="X7" s="8"/>
-      <c r="Z7" s="22"/>
-      <c r="AA7" s="22"/>
-      <c r="AB7" s="22"/>
-      <c r="AC7" s="22"/>
-      <c r="AD7" s="22"/>
-      <c r="AE7" s="22"/>
-      <c r="AF7" s="22"/>
-      <c r="AG7" s="22"/>
-    </row>
-    <row r="8" spans="2:33" x14ac:dyDescent="0.4">
+      <c r="Z7" s="21"/>
+      <c r="AA7" s="21"/>
+      <c r="AB7" s="21"/>
+      <c r="AC7" s="21"/>
+      <c r="AD7" s="21"/>
+      <c r="AE7" s="21"/>
+      <c r="AF7" s="21"/>
+      <c r="AG7" s="21"/>
+    </row>
+    <row r="8" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2" t="s">
@@ -1351,16 +1399,16 @@
       <c r="V8" s="8"/>
       <c r="W8" s="8"/>
       <c r="X8" s="8"/>
-      <c r="Z8" s="22"/>
-      <c r="AA8" s="22"/>
-      <c r="AB8" s="22"/>
-      <c r="AC8" s="22"/>
-      <c r="AD8" s="22"/>
-      <c r="AE8" s="22"/>
-      <c r="AF8" s="22"/>
-      <c r="AG8" s="22"/>
-    </row>
-    <row r="9" spans="2:33" x14ac:dyDescent="0.4">
+      <c r="Z8" s="21"/>
+      <c r="AA8" s="21"/>
+      <c r="AB8" s="21"/>
+      <c r="AC8" s="21"/>
+      <c r="AD8" s="21"/>
+      <c r="AE8" s="21"/>
+      <c r="AF8" s="21"/>
+      <c r="AG8" s="21"/>
+    </row>
+    <row r="9" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2" t="s">
@@ -1392,16 +1440,16 @@
       <c r="V9" s="8"/>
       <c r="W9" s="8"/>
       <c r="X9" s="8"/>
-      <c r="Z9" s="22"/>
-      <c r="AA9" s="22"/>
-      <c r="AB9" s="22"/>
-      <c r="AC9" s="22"/>
-      <c r="AD9" s="22"/>
-      <c r="AE9" s="22"/>
-      <c r="AF9" s="22"/>
-      <c r="AG9" s="22"/>
-    </row>
-    <row r="10" spans="2:33" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="Z9" s="21"/>
+      <c r="AA9" s="21"/>
+      <c r="AB9" s="21"/>
+      <c r="AC9" s="21"/>
+      <c r="AD9" s="21"/>
+      <c r="AE9" s="21"/>
+      <c r="AF9" s="21"/>
+      <c r="AG9" s="21"/>
+    </row>
+    <row r="10" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2" t="s">
@@ -1429,16 +1477,16 @@
       <c r="V10" s="8"/>
       <c r="W10" s="8"/>
       <c r="X10" s="8"/>
-      <c r="Z10" s="22"/>
-      <c r="AA10" s="22"/>
-      <c r="AB10" s="22"/>
-      <c r="AC10" s="22"/>
-      <c r="AD10" s="22"/>
-      <c r="AE10" s="22"/>
-      <c r="AF10" s="22"/>
-      <c r="AG10" s="22"/>
-    </row>
-    <row r="11" spans="2:33" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="Z10" s="21"/>
+      <c r="AA10" s="21"/>
+      <c r="AB10" s="21"/>
+      <c r="AC10" s="21"/>
+      <c r="AD10" s="21"/>
+      <c r="AE10" s="21"/>
+      <c r="AF10" s="21"/>
+      <c r="AG10" s="21"/>
+    </row>
+    <row r="11" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2" t="s">
@@ -1466,16 +1514,16 @@
       <c r="V11" s="8"/>
       <c r="W11" s="8"/>
       <c r="X11" s="8"/>
-      <c r="Z11" s="22"/>
-      <c r="AA11" s="22"/>
-      <c r="AB11" s="22"/>
-      <c r="AC11" s="22"/>
-      <c r="AD11" s="22"/>
-      <c r="AE11" s="22"/>
-      <c r="AF11" s="22"/>
-      <c r="AG11" s="22"/>
-    </row>
-    <row r="12" spans="2:33" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="Z11" s="21"/>
+      <c r="AA11" s="21"/>
+      <c r="AB11" s="21"/>
+      <c r="AC11" s="21"/>
+      <c r="AD11" s="21"/>
+      <c r="AE11" s="21"/>
+      <c r="AF11" s="21"/>
+      <c r="AG11" s="21"/>
+    </row>
+    <row r="12" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2" t="s">
@@ -1503,16 +1551,16 @@
       <c r="V12" s="8"/>
       <c r="W12" s="8"/>
       <c r="X12" s="8"/>
-      <c r="Z12" s="22"/>
-      <c r="AA12" s="22"/>
-      <c r="AB12" s="22"/>
-      <c r="AC12" s="22"/>
-      <c r="AD12" s="22"/>
-      <c r="AE12" s="22"/>
-      <c r="AF12" s="22"/>
-      <c r="AG12" s="22"/>
-    </row>
-    <row r="13" spans="2:33" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="Z12" s="21"/>
+      <c r="AA12" s="21"/>
+      <c r="AB12" s="21"/>
+      <c r="AC12" s="21"/>
+      <c r="AD12" s="21"/>
+      <c r="AE12" s="21"/>
+      <c r="AF12" s="21"/>
+      <c r="AG12" s="21"/>
+    </row>
+    <row r="13" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2" t="s">
@@ -1540,16 +1588,16 @@
       <c r="V13" s="8"/>
       <c r="W13" s="8"/>
       <c r="X13" s="8"/>
-      <c r="Z13" s="22"/>
-      <c r="AA13" s="22"/>
-      <c r="AB13" s="22"/>
-      <c r="AC13" s="22"/>
-      <c r="AD13" s="22"/>
-      <c r="AE13" s="22"/>
-      <c r="AF13" s="22"/>
-      <c r="AG13" s="22"/>
-    </row>
-    <row r="14" spans="2:33" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="Z13" s="21"/>
+      <c r="AA13" s="21"/>
+      <c r="AB13" s="21"/>
+      <c r="AC13" s="21"/>
+      <c r="AD13" s="21"/>
+      <c r="AE13" s="21"/>
+      <c r="AF13" s="21"/>
+      <c r="AG13" s="21"/>
+    </row>
+    <row r="14" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2" t="s">
@@ -1577,16 +1625,16 @@
       <c r="V14" s="8"/>
       <c r="W14" s="8"/>
       <c r="X14" s="8"/>
-      <c r="Z14" s="22"/>
-      <c r="AA14" s="22"/>
-      <c r="AB14" s="22"/>
-      <c r="AC14" s="22"/>
-      <c r="AD14" s="22"/>
-      <c r="AE14" s="22"/>
-      <c r="AF14" s="22"/>
-      <c r="AG14" s="22"/>
-    </row>
-    <row r="15" spans="2:33" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="Z14" s="21"/>
+      <c r="AA14" s="21"/>
+      <c r="AB14" s="21"/>
+      <c r="AC14" s="21"/>
+      <c r="AD14" s="21"/>
+      <c r="AE14" s="21"/>
+      <c r="AF14" s="21"/>
+      <c r="AG14" s="21"/>
+    </row>
+    <row r="15" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2" t="s">
@@ -1614,91 +1662,91 @@
       <c r="V15" s="8"/>
       <c r="W15" s="8"/>
       <c r="X15" s="8"/>
-      <c r="Z15" s="22"/>
-      <c r="AA15" s="22"/>
-      <c r="AB15" s="22"/>
-      <c r="AC15" s="22"/>
-      <c r="AD15" s="22"/>
-      <c r="AE15" s="22"/>
-      <c r="AF15" s="22"/>
-      <c r="AG15" s="22"/>
-    </row>
-    <row r="16" spans="2:33" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="Z15" s="21"/>
+      <c r="AA15" s="21"/>
+      <c r="AB15" s="21"/>
+      <c r="AC15" s="21"/>
+      <c r="AD15" s="21"/>
+      <c r="AE15" s="21"/>
+      <c r="AF15" s="21"/>
+      <c r="AG15" s="21"/>
+    </row>
+    <row r="16" spans="2:33" x14ac:dyDescent="0.3">
       <c r="T16" s="8"/>
       <c r="U16" s="8"/>
       <c r="V16" s="8"/>
       <c r="W16" s="8"/>
       <c r="X16" s="8"/>
-      <c r="Z16" s="22"/>
-      <c r="AA16" s="22"/>
-      <c r="AB16" s="22"/>
-      <c r="AC16" s="22"/>
-      <c r="AD16" s="22"/>
-      <c r="AE16" s="22"/>
-      <c r="AF16" s="22"/>
-      <c r="AG16" s="22"/>
-    </row>
-    <row r="17" spans="9:33" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="Z16" s="21"/>
+      <c r="AA16" s="21"/>
+      <c r="AB16" s="21"/>
+      <c r="AC16" s="21"/>
+      <c r="AD16" s="21"/>
+      <c r="AE16" s="21"/>
+      <c r="AF16" s="21"/>
+      <c r="AG16" s="21"/>
+    </row>
+    <row r="17" spans="9:33" x14ac:dyDescent="0.3">
       <c r="T17" s="8"/>
       <c r="U17" s="8"/>
       <c r="V17" s="8"/>
       <c r="W17" s="8"/>
       <c r="X17" s="8"/>
-      <c r="Z17" s="22"/>
-      <c r="AA17" s="22"/>
-      <c r="AB17" s="22"/>
-      <c r="AC17" s="22"/>
-      <c r="AD17" s="22"/>
-      <c r="AE17" s="22"/>
-      <c r="AF17" s="22"/>
-      <c r="AG17" s="22"/>
-    </row>
-    <row r="18" spans="9:33" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="Z17" s="21"/>
+      <c r="AA17" s="21"/>
+      <c r="AB17" s="21"/>
+      <c r="AC17" s="21"/>
+      <c r="AD17" s="21"/>
+      <c r="AE17" s="21"/>
+      <c r="AF17" s="21"/>
+      <c r="AG17" s="21"/>
+    </row>
+    <row r="18" spans="9:33" x14ac:dyDescent="0.3">
       <c r="T18" s="8"/>
       <c r="U18" s="8"/>
       <c r="V18" s="8"/>
       <c r="W18" s="8"/>
       <c r="X18" s="8"/>
-      <c r="Z18" s="22"/>
-      <c r="AA18" s="22"/>
-      <c r="AB18" s="22"/>
-      <c r="AC18" s="22"/>
-      <c r="AD18" s="22"/>
-      <c r="AE18" s="22"/>
-      <c r="AF18" s="22"/>
-      <c r="AG18" s="22"/>
-    </row>
-    <row r="19" spans="9:33" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="Z18" s="21"/>
+      <c r="AA18" s="21"/>
+      <c r="AB18" s="21"/>
+      <c r="AC18" s="21"/>
+      <c r="AD18" s="21"/>
+      <c r="AE18" s="21"/>
+      <c r="AF18" s="21"/>
+      <c r="AG18" s="21"/>
+    </row>
+    <row r="19" spans="9:33" x14ac:dyDescent="0.3">
       <c r="T19" s="8"/>
       <c r="U19" s="8"/>
       <c r="V19" s="8"/>
       <c r="W19" s="8"/>
       <c r="X19" s="8"/>
-      <c r="Z19" s="22"/>
-      <c r="AA19" s="22"/>
-      <c r="AB19" s="22"/>
-      <c r="AC19" s="22"/>
-      <c r="AD19" s="22"/>
-      <c r="AE19" s="22"/>
-      <c r="AF19" s="22"/>
-      <c r="AG19" s="22"/>
-    </row>
-    <row r="20" spans="9:33" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="Z19" s="21"/>
+      <c r="AA19" s="21"/>
+      <c r="AB19" s="21"/>
+      <c r="AC19" s="21"/>
+      <c r="AD19" s="21"/>
+      <c r="AE19" s="21"/>
+      <c r="AF19" s="21"/>
+      <c r="AG19" s="21"/>
+    </row>
+    <row r="20" spans="9:33" x14ac:dyDescent="0.3">
       <c r="T20" s="8"/>
       <c r="U20" s="8"/>
       <c r="V20" s="8"/>
       <c r="W20" s="8"/>
       <c r="X20" s="8"/>
-      <c r="Z20" s="22"/>
-      <c r="AA20" s="22"/>
-      <c r="AB20" s="22"/>
-      <c r="AC20" s="22"/>
-      <c r="AD20" s="22"/>
-      <c r="AE20" s="22"/>
-      <c r="AF20" s="22"/>
-      <c r="AG20" s="22"/>
-    </row>
-    <row r="21" spans="9:33" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="Z20" s="21"/>
+      <c r="AA20" s="21"/>
+      <c r="AB20" s="21"/>
+      <c r="AC20" s="21"/>
+      <c r="AD20" s="21"/>
+      <c r="AE20" s="21"/>
+      <c r="AF20" s="21"/>
+      <c r="AG20" s="21"/>
+    </row>
+    <row r="21" spans="9:33" x14ac:dyDescent="0.3">
       <c r="I21" s="10"/>
       <c r="J21" s="10"/>
       <c r="K21" s="10"/>
@@ -1713,16 +1761,16 @@
       <c r="V21" s="8"/>
       <c r="W21" s="8"/>
       <c r="X21" s="8"/>
-      <c r="Z21" s="22"/>
-      <c r="AA21" s="22"/>
-      <c r="AB21" s="22"/>
-      <c r="AC21" s="22"/>
-      <c r="AD21" s="22"/>
-      <c r="AE21" s="22"/>
-      <c r="AF21" s="22"/>
-      <c r="AG21" s="22"/>
-    </row>
-    <row r="22" spans="9:33" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="Z21" s="21"/>
+      <c r="AA21" s="21"/>
+      <c r="AB21" s="21"/>
+      <c r="AC21" s="21"/>
+      <c r="AD21" s="21"/>
+      <c r="AE21" s="21"/>
+      <c r="AF21" s="21"/>
+      <c r="AG21" s="21"/>
+    </row>
+    <row r="22" spans="9:33" x14ac:dyDescent="0.3">
       <c r="I22" s="11"/>
       <c r="J22" s="11"/>
       <c r="K22" s="11"/>
@@ -1737,16 +1785,16 @@
       <c r="V22" s="8"/>
       <c r="W22" s="8"/>
       <c r="X22" s="8"/>
-      <c r="Z22" s="22"/>
-      <c r="AA22" s="22"/>
-      <c r="AB22" s="22"/>
-      <c r="AC22" s="22"/>
-      <c r="AD22" s="22"/>
-      <c r="AE22" s="22"/>
-      <c r="AF22" s="22"/>
-      <c r="AG22" s="22"/>
-    </row>
-    <row r="23" spans="9:33" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="Z22" s="21"/>
+      <c r="AA22" s="21"/>
+      <c r="AB22" s="21"/>
+      <c r="AC22" s="21"/>
+      <c r="AD22" s="21"/>
+      <c r="AE22" s="21"/>
+      <c r="AF22" s="21"/>
+      <c r="AG22" s="21"/>
+    </row>
+    <row r="23" spans="9:33" x14ac:dyDescent="0.3">
       <c r="I23" s="11"/>
       <c r="J23" s="11"/>
       <c r="K23" s="11"/>
@@ -1761,16 +1809,16 @@
       <c r="V23" s="8"/>
       <c r="W23" s="8"/>
       <c r="X23" s="8"/>
-      <c r="Z23" s="22"/>
-      <c r="AA23" s="22"/>
-      <c r="AB23" s="22"/>
-      <c r="AC23" s="22"/>
-      <c r="AD23" s="22"/>
-      <c r="AE23" s="22"/>
-      <c r="AF23" s="22"/>
-      <c r="AG23" s="22"/>
-    </row>
-    <row r="24" spans="9:33" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="Z23" s="21"/>
+      <c r="AA23" s="21"/>
+      <c r="AB23" s="21"/>
+      <c r="AC23" s="21"/>
+      <c r="AD23" s="21"/>
+      <c r="AE23" s="21"/>
+      <c r="AF23" s="21"/>
+      <c r="AG23" s="21"/>
+    </row>
+    <row r="24" spans="9:33" x14ac:dyDescent="0.3">
       <c r="I24" s="11"/>
       <c r="J24" s="11"/>
       <c r="K24" s="11"/>
@@ -1781,7 +1829,7 @@
       <c r="P24" s="11"/>
       <c r="Q24" s="11"/>
     </row>
-    <row r="25" spans="9:33" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="25" spans="9:33" x14ac:dyDescent="0.3">
       <c r="I25" s="11"/>
       <c r="J25" s="11"/>
       <c r="K25" s="11"/>
@@ -1792,7 +1840,7 @@
       <c r="P25" s="11"/>
       <c r="Q25" s="11"/>
     </row>
-    <row r="26" spans="9:33" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="26" spans="9:33" x14ac:dyDescent="0.3">
       <c r="I26" s="11"/>
       <c r="J26" s="11"/>
       <c r="K26" s="11"/>
@@ -1803,7 +1851,7 @@
       <c r="P26" s="11"/>
       <c r="Q26" s="11"/>
     </row>
-    <row r="27" spans="9:33" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="27" spans="9:33" x14ac:dyDescent="0.3">
       <c r="I27" s="11"/>
       <c r="J27" s="11"/>
       <c r="K27" s="11"/>
@@ -1814,7 +1862,7 @@
       <c r="P27" s="11"/>
       <c r="Q27" s="11"/>
     </row>
-    <row r="28" spans="9:33" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="28" spans="9:33" x14ac:dyDescent="0.3">
       <c r="I28" s="11"/>
       <c r="J28" s="11"/>
       <c r="K28" s="11"/>
@@ -1825,7 +1873,7 @@
       <c r="P28" s="11"/>
       <c r="Q28" s="11"/>
     </row>
-    <row r="29" spans="9:33" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="29" spans="9:33" x14ac:dyDescent="0.3">
       <c r="I29" s="11"/>
       <c r="J29" s="11"/>
       <c r="K29" s="11"/>
@@ -1836,7 +1884,7 @@
       <c r="P29" s="11"/>
       <c r="Q29" s="11"/>
     </row>
-    <row r="30" spans="9:33" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="30" spans="9:33" x14ac:dyDescent="0.3">
       <c r="I30" s="11"/>
       <c r="J30" s="11"/>
       <c r="K30" s="11"/>
@@ -1847,7 +1895,7 @@
       <c r="P30" s="11"/>
       <c r="Q30" s="11"/>
     </row>
-    <row r="31" spans="9:33" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="31" spans="9:33" x14ac:dyDescent="0.3">
       <c r="I31" s="11"/>
       <c r="J31" s="11"/>
       <c r="K31" s="11"/>
@@ -1858,7 +1906,7 @@
       <c r="P31" s="11"/>
       <c r="Q31" s="11"/>
     </row>
-    <row r="32" spans="9:33" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="32" spans="9:33" x14ac:dyDescent="0.3">
       <c r="I32" s="11"/>
       <c r="J32" s="11"/>
       <c r="K32" s="11"/>
@@ -1869,7 +1917,7 @@
       <c r="P32" s="11"/>
       <c r="Q32" s="11"/>
     </row>
-    <row r="33" spans="9:17" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="33" spans="9:17" x14ac:dyDescent="0.3">
       <c r="I33" s="11"/>
       <c r="J33" s="11"/>
       <c r="K33" s="11"/>
@@ -1880,7 +1928,7 @@
       <c r="P33" s="11"/>
       <c r="Q33" s="11"/>
     </row>
-    <row r="34" spans="9:17" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="34" spans="9:17" x14ac:dyDescent="0.3">
       <c r="I34" s="11"/>
       <c r="J34" s="11"/>
       <c r="K34" s="11"/>
@@ -1891,7 +1939,7 @@
       <c r="P34" s="11"/>
       <c r="Q34" s="11"/>
     </row>
-    <row r="35" spans="9:17" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="35" spans="9:17" x14ac:dyDescent="0.3">
       <c r="I35" s="11"/>
       <c r="J35" s="11"/>
       <c r="K35" s="11"/>
@@ -1902,7 +1950,7 @@
       <c r="P35" s="11"/>
       <c r="Q35" s="11"/>
     </row>
-    <row r="36" spans="9:17" x14ac:dyDescent="0.4">
+    <row r="36" spans="9:17" x14ac:dyDescent="0.3">
       <c r="I36" s="11"/>
       <c r="J36" s="11"/>
       <c r="K36" s="11"/>
@@ -1913,7 +1961,7 @@
       <c r="P36" s="11"/>
       <c r="Q36" s="11"/>
     </row>
-    <row r="37" spans="9:17" x14ac:dyDescent="0.4">
+    <row r="37" spans="9:17" x14ac:dyDescent="0.3">
       <c r="I37" s="11"/>
       <c r="J37" s="11"/>
       <c r="K37" s="11"/>
@@ -1924,7 +1972,7 @@
       <c r="P37" s="11"/>
       <c r="Q37" s="11"/>
     </row>
-    <row r="38" spans="9:17" x14ac:dyDescent="0.4">
+    <row r="38" spans="9:17" x14ac:dyDescent="0.3">
       <c r="I38" s="11"/>
       <c r="J38" s="11"/>
       <c r="K38" s="11"/>
@@ -1935,7 +1983,7 @@
       <c r="P38" s="11"/>
       <c r="Q38" s="11"/>
     </row>
-    <row r="39" spans="9:17" x14ac:dyDescent="0.4">
+    <row r="39" spans="9:17" x14ac:dyDescent="0.3">
       <c r="I39" s="11"/>
       <c r="J39" s="11"/>
       <c r="K39" s="11"/>
@@ -1946,7 +1994,7 @@
       <c r="P39" s="11"/>
       <c r="Q39" s="11"/>
     </row>
-    <row r="40" spans="9:17" x14ac:dyDescent="0.4">
+    <row r="40" spans="9:17" x14ac:dyDescent="0.3">
       <c r="I40" s="12"/>
       <c r="J40" s="12"/>
       <c r="K40" s="12"/>
@@ -1965,24 +2013,33 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:G14"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="B2:N14"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="63" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.19921875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B2" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="F2" t="s">
+      <c r="D2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F2" s="22" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="3" spans="2:7" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="K2" s="13" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B3" s="15" t="s">
         <v>87</v>
       </c>
@@ -1992,12 +2049,32 @@
       <c r="D3" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="F3" s="20" t="s">
-        <v>91</v>
-      </c>
-      <c r="G3" s="20"/>
-    </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="F3" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="G3" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="H3" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="I3" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="K3" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="L3" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="M3" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="N3" s="13" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B4" s="18"/>
       <c r="C4" s="18" t="s">
         <v>88</v>
@@ -2005,8 +2082,16 @@
       <c r="D4" s="18">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.4">
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="18"/>
+      <c r="K4" s="18"/>
+      <c r="L4" s="18"/>
+      <c r="M4" s="18"/>
+      <c r="N4" s="18"/>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B5" s="18"/>
       <c r="C5" s="18" t="s">
         <v>89</v>
@@ -2014,62 +2099,143 @@
       <c r="D5" s="18">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="2:7" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="18"/>
+      <c r="K5" s="18"/>
+      <c r="L5" s="18"/>
+      <c r="M5" s="18"/>
+      <c r="N5" s="18"/>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
       <c r="D6" s="18"/>
-    </row>
-    <row r="7" spans="2:7" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="18"/>
+      <c r="M6" s="18"/>
+      <c r="N6" s="18"/>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B7" s="18"/>
       <c r="C7" s="18"/>
       <c r="D7" s="18"/>
-    </row>
-    <row r="8" spans="2:7" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="F7" s="18"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="18"/>
+      <c r="K7" s="18"/>
+      <c r="L7" s="18"/>
+      <c r="M7" s="18"/>
+      <c r="N7" s="18"/>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B8" s="18"/>
       <c r="C8" s="18"/>
       <c r="D8" s="18"/>
-    </row>
-    <row r="9" spans="2:7" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="18"/>
+      <c r="K8" s="18"/>
+      <c r="L8" s="18"/>
+      <c r="M8" s="18"/>
+      <c r="N8" s="18"/>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B9" s="18"/>
       <c r="C9" s="18"/>
       <c r="D9" s="18"/>
-    </row>
-    <row r="10" spans="2:7" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="18"/>
+      <c r="K9" s="18"/>
+      <c r="L9" s="18"/>
+      <c r="M9" s="18"/>
+      <c r="N9" s="18"/>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B10" s="18"/>
       <c r="C10" s="18"/>
       <c r="D10" s="18"/>
-    </row>
-    <row r="11" spans="2:7" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="18"/>
+      <c r="K10" s="18"/>
+      <c r="L10" s="18"/>
+      <c r="M10" s="18"/>
+      <c r="N10" s="18"/>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B11" s="18"/>
       <c r="C11" s="18"/>
       <c r="D11" s="18"/>
-    </row>
-    <row r="12" spans="2:7" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="18"/>
+      <c r="K11" s="18"/>
+      <c r="L11" s="18"/>
+      <c r="M11" s="18"/>
+      <c r="N11" s="18"/>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B12" s="18"/>
       <c r="C12" s="18"/>
       <c r="D12" s="18"/>
-    </row>
-    <row r="13" spans="2:7" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="18"/>
+      <c r="I12" s="18"/>
+      <c r="K12" s="18"/>
+      <c r="L12" s="18"/>
+      <c r="M12" s="18"/>
+      <c r="N12" s="18"/>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B13" s="18"/>
       <c r="C13" s="18"/>
       <c r="D13" s="18"/>
-    </row>
-    <row r="14" spans="2:7" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="18"/>
+      <c r="K13" s="18"/>
+      <c r="L13" s="18"/>
+      <c r="M13" s="18"/>
+      <c r="N13" s="18"/>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B14" s="18"/>
       <c r="C14" s="18"/>
       <c r="D14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="18"/>
+      <c r="I14" s="18"/>
+      <c r="K14" s="18"/>
+      <c r="L14" s="18"/>
+      <c r="M14" s="18"/>
+      <c r="N14" s="18"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2077,9 +2243,9 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/planningPhase/heartpigeon/heartpigeon_DB.xlsx
+++ b/planningPhase/heartpigeon/heartpigeon_DB.xlsx
@@ -1,22 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TJ-BU-702-24PC\Desktop\cording\kafella92.github.io\planningPhase\heartpigeon\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26529F8B-9021-4B35-881E-CA1FC292CE80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1956" yWindow="1956" windowWidth="21600" windowHeight="11388" firstSheet="1" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="DB(user_gift)" sheetId="1" r:id="rId1"/>
     <sheet name="DB(mindtest)" sheetId="4" r:id="rId2"/>
-    <sheet name="normalization(mindtest)" sheetId="2" r:id="rId3"/>
-    <sheet name="Sheet2" sheetId="3" r:id="rId4"/>
+    <sheet name="sample" sheetId="3" r:id="rId3"/>
+    <sheet name="normalization(mindtest)" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="144525"/>
   <extLst>
@@ -465,7 +459,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1010,37 +1004,37 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:AG40"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="17.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.875" customWidth="1"/>
+    <col min="2" max="2" width="17.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.8984375" customWidth="1"/>
     <col min="5" max="5" width="11.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="21" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.75" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.625" customWidth="1"/>
-    <col min="11" max="11" width="12.375" customWidth="1"/>
-    <col min="14" max="14" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="23.125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.69921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.59765625" customWidth="1"/>
+    <col min="11" max="11" width="12.3984375" customWidth="1"/>
+    <col min="14" max="14" width="12.69921875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.09765625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.59765625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="23.09765625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.09765625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.19921875" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="34.5" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="17.375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="23.75" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.19921875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="17.3984375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="23.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:33" x14ac:dyDescent="0.4">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1084,7 +1078,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="3" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:33" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
@@ -1159,7 +1153,7 @@
       <c r="AF3" s="20"/>
       <c r="AG3" s="20"/>
     </row>
-    <row r="4" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:33" x14ac:dyDescent="0.4">
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
@@ -1212,7 +1206,7 @@
       <c r="AF4" s="21"/>
       <c r="AG4" s="21"/>
     </row>
-    <row r="5" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:33" x14ac:dyDescent="0.4">
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2" t="s">
@@ -1265,7 +1259,7 @@
       <c r="AF5" s="21"/>
       <c r="AG5" s="21"/>
     </row>
-    <row r="6" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:33" x14ac:dyDescent="0.4">
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2" t="s">
@@ -1318,7 +1312,7 @@
       <c r="AF6" s="21"/>
       <c r="AG6" s="21"/>
     </row>
-    <row r="7" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:33" x14ac:dyDescent="0.4">
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2" t="s">
@@ -1365,7 +1359,7 @@
       <c r="AF7" s="21"/>
       <c r="AG7" s="21"/>
     </row>
-    <row r="8" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:33" x14ac:dyDescent="0.4">
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2" t="s">
@@ -1408,7 +1402,7 @@
       <c r="AF8" s="21"/>
       <c r="AG8" s="21"/>
     </row>
-    <row r="9" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:33" x14ac:dyDescent="0.4">
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2" t="s">
@@ -1449,7 +1443,7 @@
       <c r="AF9" s="21"/>
       <c r="AG9" s="21"/>
     </row>
-    <row r="10" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:33" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2" t="s">
@@ -1486,7 +1480,7 @@
       <c r="AF10" s="21"/>
       <c r="AG10" s="21"/>
     </row>
-    <row r="11" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:33" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2" t="s">
@@ -1523,7 +1517,7 @@
       <c r="AF11" s="21"/>
       <c r="AG11" s="21"/>
     </row>
-    <row r="12" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:33" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2" t="s">
@@ -1560,7 +1554,7 @@
       <c r="AF12" s="21"/>
       <c r="AG12" s="21"/>
     </row>
-    <row r="13" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:33" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2" t="s">
@@ -1597,7 +1591,7 @@
       <c r="AF13" s="21"/>
       <c r="AG13" s="21"/>
     </row>
-    <row r="14" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:33" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2" t="s">
@@ -1634,7 +1628,7 @@
       <c r="AF14" s="21"/>
       <c r="AG14" s="21"/>
     </row>
-    <row r="15" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:33" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2" t="s">
@@ -1671,7 +1665,7 @@
       <c r="AF15" s="21"/>
       <c r="AG15" s="21"/>
     </row>
-    <row r="16" spans="2:33" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:33" ht="16.5" x14ac:dyDescent="0.3">
       <c r="T16" s="8"/>
       <c r="U16" s="8"/>
       <c r="V16" s="8"/>
@@ -1686,7 +1680,7 @@
       <c r="AF16" s="21"/>
       <c r="AG16" s="21"/>
     </row>
-    <row r="17" spans="9:33" x14ac:dyDescent="0.3">
+    <row r="17" spans="9:33" ht="16.5" x14ac:dyDescent="0.3">
       <c r="T17" s="8"/>
       <c r="U17" s="8"/>
       <c r="V17" s="8"/>
@@ -1701,7 +1695,7 @@
       <c r="AF17" s="21"/>
       <c r="AG17" s="21"/>
     </row>
-    <row r="18" spans="9:33" x14ac:dyDescent="0.3">
+    <row r="18" spans="9:33" ht="16.5" x14ac:dyDescent="0.3">
       <c r="T18" s="8"/>
       <c r="U18" s="8"/>
       <c r="V18" s="8"/>
@@ -1716,7 +1710,7 @@
       <c r="AF18" s="21"/>
       <c r="AG18" s="21"/>
     </row>
-    <row r="19" spans="9:33" x14ac:dyDescent="0.3">
+    <row r="19" spans="9:33" ht="16.5" x14ac:dyDescent="0.3">
       <c r="T19" s="8"/>
       <c r="U19" s="8"/>
       <c r="V19" s="8"/>
@@ -1731,7 +1725,7 @@
       <c r="AF19" s="21"/>
       <c r="AG19" s="21"/>
     </row>
-    <row r="20" spans="9:33" x14ac:dyDescent="0.3">
+    <row r="20" spans="9:33" ht="16.5" x14ac:dyDescent="0.3">
       <c r="T20" s="8"/>
       <c r="U20" s="8"/>
       <c r="V20" s="8"/>
@@ -1746,7 +1740,7 @@
       <c r="AF20" s="21"/>
       <c r="AG20" s="21"/>
     </row>
-    <row r="21" spans="9:33" x14ac:dyDescent="0.3">
+    <row r="21" spans="9:33" ht="16.5" x14ac:dyDescent="0.3">
       <c r="I21" s="10"/>
       <c r="J21" s="10"/>
       <c r="K21" s="10"/>
@@ -1770,7 +1764,7 @@
       <c r="AF21" s="21"/>
       <c r="AG21" s="21"/>
     </row>
-    <row r="22" spans="9:33" x14ac:dyDescent="0.3">
+    <row r="22" spans="9:33" ht="16.5" x14ac:dyDescent="0.3">
       <c r="I22" s="11"/>
       <c r="J22" s="11"/>
       <c r="K22" s="11"/>
@@ -1794,7 +1788,7 @@
       <c r="AF22" s="21"/>
       <c r="AG22" s="21"/>
     </row>
-    <row r="23" spans="9:33" x14ac:dyDescent="0.3">
+    <row r="23" spans="9:33" ht="16.5" x14ac:dyDescent="0.3">
       <c r="I23" s="11"/>
       <c r="J23" s="11"/>
       <c r="K23" s="11"/>
@@ -1818,7 +1812,7 @@
       <c r="AF23" s="21"/>
       <c r="AG23" s="21"/>
     </row>
-    <row r="24" spans="9:33" x14ac:dyDescent="0.3">
+    <row r="24" spans="9:33" ht="16.5" x14ac:dyDescent="0.3">
       <c r="I24" s="11"/>
       <c r="J24" s="11"/>
       <c r="K24" s="11"/>
@@ -1829,7 +1823,7 @@
       <c r="P24" s="11"/>
       <c r="Q24" s="11"/>
     </row>
-    <row r="25" spans="9:33" x14ac:dyDescent="0.3">
+    <row r="25" spans="9:33" ht="16.5" x14ac:dyDescent="0.3">
       <c r="I25" s="11"/>
       <c r="J25" s="11"/>
       <c r="K25" s="11"/>
@@ -1840,7 +1834,7 @@
       <c r="P25" s="11"/>
       <c r="Q25" s="11"/>
     </row>
-    <row r="26" spans="9:33" x14ac:dyDescent="0.3">
+    <row r="26" spans="9:33" ht="16.5" x14ac:dyDescent="0.3">
       <c r="I26" s="11"/>
       <c r="J26" s="11"/>
       <c r="K26" s="11"/>
@@ -1851,7 +1845,7 @@
       <c r="P26" s="11"/>
       <c r="Q26" s="11"/>
     </row>
-    <row r="27" spans="9:33" x14ac:dyDescent="0.3">
+    <row r="27" spans="9:33" ht="16.5" x14ac:dyDescent="0.3">
       <c r="I27" s="11"/>
       <c r="J27" s="11"/>
       <c r="K27" s="11"/>
@@ -1862,7 +1856,7 @@
       <c r="P27" s="11"/>
       <c r="Q27" s="11"/>
     </row>
-    <row r="28" spans="9:33" x14ac:dyDescent="0.3">
+    <row r="28" spans="9:33" ht="16.5" x14ac:dyDescent="0.3">
       <c r="I28" s="11"/>
       <c r="J28" s="11"/>
       <c r="K28" s="11"/>
@@ -1873,7 +1867,7 @@
       <c r="P28" s="11"/>
       <c r="Q28" s="11"/>
     </row>
-    <row r="29" spans="9:33" x14ac:dyDescent="0.3">
+    <row r="29" spans="9:33" ht="16.5" x14ac:dyDescent="0.3">
       <c r="I29" s="11"/>
       <c r="J29" s="11"/>
       <c r="K29" s="11"/>
@@ -1884,7 +1878,7 @@
       <c r="P29" s="11"/>
       <c r="Q29" s="11"/>
     </row>
-    <row r="30" spans="9:33" x14ac:dyDescent="0.3">
+    <row r="30" spans="9:33" ht="16.5" x14ac:dyDescent="0.3">
       <c r="I30" s="11"/>
       <c r="J30" s="11"/>
       <c r="K30" s="11"/>
@@ -1895,7 +1889,7 @@
       <c r="P30" s="11"/>
       <c r="Q30" s="11"/>
     </row>
-    <row r="31" spans="9:33" x14ac:dyDescent="0.3">
+    <row r="31" spans="9:33" ht="16.5" x14ac:dyDescent="0.3">
       <c r="I31" s="11"/>
       <c r="J31" s="11"/>
       <c r="K31" s="11"/>
@@ -1906,7 +1900,7 @@
       <c r="P31" s="11"/>
       <c r="Q31" s="11"/>
     </row>
-    <row r="32" spans="9:33" x14ac:dyDescent="0.3">
+    <row r="32" spans="9:33" ht="16.5" x14ac:dyDescent="0.3">
       <c r="I32" s="11"/>
       <c r="J32" s="11"/>
       <c r="K32" s="11"/>
@@ -1917,7 +1911,7 @@
       <c r="P32" s="11"/>
       <c r="Q32" s="11"/>
     </row>
-    <row r="33" spans="9:17" x14ac:dyDescent="0.3">
+    <row r="33" spans="9:17" ht="16.5" x14ac:dyDescent="0.3">
       <c r="I33" s="11"/>
       <c r="J33" s="11"/>
       <c r="K33" s="11"/>
@@ -1928,7 +1922,7 @@
       <c r="P33" s="11"/>
       <c r="Q33" s="11"/>
     </row>
-    <row r="34" spans="9:17" x14ac:dyDescent="0.3">
+    <row r="34" spans="9:17" ht="16.5" x14ac:dyDescent="0.3">
       <c r="I34" s="11"/>
       <c r="J34" s="11"/>
       <c r="K34" s="11"/>
@@ -1939,7 +1933,7 @@
       <c r="P34" s="11"/>
       <c r="Q34" s="11"/>
     </row>
-    <row r="35" spans="9:17" x14ac:dyDescent="0.3">
+    <row r="35" spans="9:17" ht="16.5" x14ac:dyDescent="0.3">
       <c r="I35" s="11"/>
       <c r="J35" s="11"/>
       <c r="K35" s="11"/>
@@ -1950,7 +1944,7 @@
       <c r="P35" s="11"/>
       <c r="Q35" s="11"/>
     </row>
-    <row r="36" spans="9:17" x14ac:dyDescent="0.3">
+    <row r="36" spans="9:17" x14ac:dyDescent="0.4">
       <c r="I36" s="11"/>
       <c r="J36" s="11"/>
       <c r="K36" s="11"/>
@@ -1961,7 +1955,7 @@
       <c r="P36" s="11"/>
       <c r="Q36" s="11"/>
     </row>
-    <row r="37" spans="9:17" x14ac:dyDescent="0.3">
+    <row r="37" spans="9:17" x14ac:dyDescent="0.4">
       <c r="I37" s="11"/>
       <c r="J37" s="11"/>
       <c r="K37" s="11"/>
@@ -1972,7 +1966,7 @@
       <c r="P37" s="11"/>
       <c r="Q37" s="11"/>
     </row>
-    <row r="38" spans="9:17" x14ac:dyDescent="0.3">
+    <row r="38" spans="9:17" x14ac:dyDescent="0.4">
       <c r="I38" s="11"/>
       <c r="J38" s="11"/>
       <c r="K38" s="11"/>
@@ -1983,7 +1977,7 @@
       <c r="P38" s="11"/>
       <c r="Q38" s="11"/>
     </row>
-    <row r="39" spans="9:17" x14ac:dyDescent="0.3">
+    <row r="39" spans="9:17" x14ac:dyDescent="0.4">
       <c r="I39" s="11"/>
       <c r="J39" s="11"/>
       <c r="K39" s="11"/>
@@ -1994,7 +1988,7 @@
       <c r="P39" s="11"/>
       <c r="Q39" s="11"/>
     </row>
-    <row r="40" spans="9:17" x14ac:dyDescent="0.3">
+    <row r="40" spans="9:17" x14ac:dyDescent="0.4">
       <c r="I40" s="12"/>
       <c r="J40" s="12"/>
       <c r="K40" s="12"/>
@@ -2013,19 +2007,19 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:N14"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="63" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.19921875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="16" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.59765625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="10.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B2" s="19" t="s">
         <v>84</v>
       </c>
@@ -2039,7 +2033,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B3" s="15" t="s">
         <v>87</v>
       </c>
@@ -2074,7 +2068,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B4" s="18"/>
       <c r="C4" s="18" t="s">
         <v>88</v>
@@ -2091,7 +2085,7 @@
       <c r="M4" s="18"/>
       <c r="N4" s="18"/>
     </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B5" s="18"/>
       <c r="C5" s="18" t="s">
         <v>89</v>
@@ -2108,7 +2102,7 @@
       <c r="M5" s="18"/>
       <c r="N5" s="18"/>
     </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
       <c r="D6" s="18"/>
@@ -2121,7 +2115,7 @@
       <c r="M6" s="18"/>
       <c r="N6" s="18"/>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B7" s="18"/>
       <c r="C7" s="18"/>
       <c r="D7" s="18"/>
@@ -2134,7 +2128,7 @@
       <c r="M7" s="18"/>
       <c r="N7" s="18"/>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B8" s="18"/>
       <c r="C8" s="18"/>
       <c r="D8" s="18"/>
@@ -2147,7 +2141,7 @@
       <c r="M8" s="18"/>
       <c r="N8" s="18"/>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B9" s="18"/>
       <c r="C9" s="18"/>
       <c r="D9" s="18"/>
@@ -2160,7 +2154,7 @@
       <c r="M9" s="18"/>
       <c r="N9" s="18"/>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B10" s="18"/>
       <c r="C10" s="18"/>
       <c r="D10" s="18"/>
@@ -2173,7 +2167,7 @@
       <c r="M10" s="18"/>
       <c r="N10" s="18"/>
     </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B11" s="18"/>
       <c r="C11" s="18"/>
       <c r="D11" s="18"/>
@@ -2186,7 +2180,7 @@
       <c r="M11" s="18"/>
       <c r="N11" s="18"/>
     </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B12" s="18"/>
       <c r="C12" s="18"/>
       <c r="D12" s="18"/>
@@ -2199,7 +2193,7 @@
       <c r="M12" s="18"/>
       <c r="N12" s="18"/>
     </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B13" s="18"/>
       <c r="C13" s="18"/>
       <c r="D13" s="18"/>
@@ -2212,7 +2206,7 @@
       <c r="M13" s="18"/>
       <c r="N13" s="18"/>
     </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:14" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B14" s="18"/>
       <c r="C14" s="18"/>
       <c r="D14" s="18"/>
@@ -2233,9 +2227,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2243,9 +2237,9 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
